--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -1608,12 +1608,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例）</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1633,19 +1633,19 @@
         <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>行业层面订单与产能回流中国，直接实例</t>
+          <t>富士康撤回印度工程团队、重新评估海外布局，「订单/产能回流中国」未获证实，部分相关 ｜ 人工判定与Auto(2)不同，请复核</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publisher: 路透社（经环球网 / 新浪转载） Country/Jurisdiction: CN/VN/TH/IN Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用制造 Claim: 部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形</t>
+          <t>Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） Publisher: 新浪科技 / 中关村在线 Country/Jurisdiction: TW/CN/IN Publication date: 2025-07-03 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电子制造 Claim: 2025 年 7 月及 12 月，富士康两度要求/</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1704,25 +1704,25 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>泰国建厂案例，非回流 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>行业层面订单与产能回流中国，直接实例</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publisher: 路透社（经环球网 / 新浪转载） Country/Jurisdiction: CN/VN/TH/IN Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用制造 Claim: 部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4164,29 +4164,29 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>欧洲业务收缩，与该假设无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>终止马来西亚项目，与该假设无关 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4241,29 +4241,29 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>终止马来西亚项目，与该假设无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>欧洲业务收缩，与该假设无关 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
         </is>
       </c>
     </row>
@@ -6921,12 +6921,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>越南基地正负极材料仍来自中国，依赖例证</t>
+          <t>欣旺达越南基地：越南建厂但仍依赖中国材料，依赖例证</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>东方财富网 / 腾讯新闻</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
+          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>越南基地材料仍由中国供应，依赖例证</t>
+          <t>国轩高科越南基地：正负极材料仍来自中国，依赖例证</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>澎湃新闻 / 盖世汽车社区</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ##</t>
+          <t>## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ##</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ##</t>
+          <t>## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ##</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A4,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>新增4个回流/撤出案例，回流实例充足</t>
+          <t>回流/撤出案例充足；RETURN_002 因「回流」未证实记为部分相关，不影响覆盖</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_003; RELOC_006</t>
+          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>判例仅命中2条（CASE_002/CASE_010），缺终裁原文与未规避对照</t>
+          <t>判例仅命中2条（CASE_002/CASE_010），第2/3名案例证据与该假设无关</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_004; RETURN_001; CASE_010; RELOC_005</t>
+          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_003; RELOC_005; WH_002</t>
+          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -13924,6 +13924,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -14012,6 +14013,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -14031,18 +14033,6 @@
         </is>
       </c>
       <c r="B12" t="inlineStr">
-        <is>
-          <t>AI-assisted pre-scoring (content-based). Review flagged rows before finalising.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Scoring pass</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
         <is>
           <t>AI-assisted pre-scoring (content-based). Review flagged rows before finalising.</t>
         </is>

--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -607,12 +607,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_005</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>新易盛：2022年设立泰国基地，一二期已投产</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源泰国电池工厂已投产，直接案例</t>
+          <t>新易盛泰国基地一二期已投产，直接案例</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -703,25 +703,25 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>欧洲业务收缩，与泰国建厂无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>中际旭创泰国工厂产能与国内齐平，直接案例</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -786,19 +786,19 @@
         <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>国轩为越南基地，非泰国 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>Dawang Metals 为订单转印度后回流案例，可作建厂节奏反向参照，但非泰国布局</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 / 盖世汽车社区 Country/Jurisdiction: CN/VN Publication date: 2022-11-19 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 与 Vingroup 旗下 VinES 合资（国轩 51% / VinE</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -853,29 +853,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>长安泰国整车工厂投产，直接案例</t>
+          <t>天孚通信泰国一期投产、二期2025启用，直接案例</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_002 Title: 长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） Publisher: 易车 / 证券之星（投资者互动平台） Country/Jurisdiction: CN/TH Publication date: 2025-05-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 整车/汽车 Claim: 在泰国罗勇府建设整车工厂，2025-05-16 竣工投产</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -930,29 +930,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>比亚迪泰国整车工厂投产，直接案例</t>
+          <t>光模块厂商东南亚建厂以规避欧美客户合作风险，直接说明泰国布局</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_001 Title: 比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网（转比亚迪官方） Country/Jurisdiction: CN/TH Publication date: 2024-07-04 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 整车/汽车 Claim: 2022-09 与 WHA 签约，在泰国罗勇府建全资乘用车工厂；2024-07-04 竣工投产，年</t>
+          <t>中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一份“炸裂”的半年业绩预告。 数据显示，中际旭创预计上半年实现归母净利润21. 5亿元-25亿元，增长幅度上限超300%，而业绩下限水平甚至已可比肩去年全年。 半年业绩或超去年全年 中际旭创业绩预告显示，该公司预计上半年实现净利润21. 5亿元-25亿元，同比增长250. 3%-307. 33%。 而且，中际旭创还称，今年上半年确认股权激励费用减少公司合并净利润约9300万元。 对于上半年业绩大幅增长，中际旭创解释</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1007,29 +1007,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>恩捷终止马来西亚项目：马来西亚布局决策的直接案例</t>
+          <t>华工正源马来西亚工厂，公开表述为规避地缘风险，直接案例</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能马来西亚工厂投产，直接案例</t>
+          <t>白宫点名东南亚（含马来西亚）为转运高风险，美国官方判断</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: CASE_010 Title: 白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 Publisher: 美国白宫（经律所解读） Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 由WH_001与WH_002组成。对已在越南/泰国/马来西亚布局的企业，原产地举证</t>
         </is>
       </c>
     </row>
@@ -1146,44 +1146,44 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>华工正源马来西亚工厂，公开表述为规避地缘风险，直接案例</t>
+          <t>美国商务部反规避认定（含马来西亚企业），直接反映美方对马来西亚原产地的官方判断 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -1223,44 +1223,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_004</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：China + 1 战略（多地区混合布局）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>晶科含马来西亚枢纽，但为光伏多地区结构，非马来西亚布局主案例 ｜ 人工判定与Auto(2)不同，请复核</t>
+          <t>美国商务部认定东南亚四国光伏视为中国原产，直接反映美方对马来西亚原产地的官方判断 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>东方财富财富号</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：硅片—电池—组件一体化产能以中国为核心。 主要市场：全球（中国、欧洲、美国、新兴市场）。 供应链结构：硅料、硅片主要在中国，组件通过海外基地与出口进入欧美。 面临的问题：美国对东南亚四国光伏产品的双反与反规避调查，使'中国—东南亚—美国'路径的关税优势不稳定（参见 Task 1 的 CASE_002/CASE_003）。 ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对东南亚光伏组件的双反/反规避认定，以及美</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -1300,44 +1300,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚（含马来西亚）为转运高风险，美国官方判断</t>
+          <t>中国对马/越/泰中间品出口数据，间接支持企业马来西亚布局判断</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_010 Title: 白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 Publisher: 美国白宫（经律所解读） Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 由WH_001与WH_002组成。对已在越南/泰国/马来西亚布局的企业，原产地举证</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1469,29 +1469,29 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>终止马来西亚项目、资源回投国内，直接回流实例</t>
+          <t>东南亚建厂规避风险案例，与「回流中国」方向相反，仅作同类布局参照</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_001 Title: 恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） Publisher: 恩捷股份公告（经东方财富网 / 央广网报道） Country/Jurisdiction: CN/MY Publication date: 2026-05-22 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电池材料 Claim: 2026</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1550,25 +1550,25 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>停建德国工厂、终止欧洲业务，资源集中中国，直接实例</t>
+          <t>马来西亚工厂案例，与「回流中国」方向相反，仅作同类布局参照</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>在AI算力基础设施持续扩张的背景下，具备高速率产品量产能力、全球化交付能力与核心器件自研能力的厂商，将在下一阶段竞争中占据主动。 对于下游客户而言，根据自身场景需求在“规模稳定”、“性价比”、“行业定制”三者之间做出选择，已成为当前光模块采购决策的关键。 C114中国通信网版权说明：凡注明来源为“C114通信网”的文章皆属C114版权所有，除与C114签署内容授权协议的单位外，其他单位未经允许禁止转载、摘编，违者必究。 如需使用，请联系021-54451141（汪先生）。 其中编译类仅出于传递更多信息之目的，系C114对海外相关站点最新信息的翻译稿，仅供</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1</v>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>富士康撤回印度工程团队、重新评估海外布局，「订单/产能回流中国」未获证实，部分相关 ｜ 人工判定与Auto(2)不同，请复核</t>
+          <t>泰国工厂案例，与「回流中国」方向相反，仅作同类布局参照</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） Publisher: 新浪科技 / 中关村在线 Country/Jurisdiction: TW/CN/IN Publication date: 2025-07-03 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电子制造 Claim: 2025 年 7 月及 12 月，富士康两度要求/</t>
+          <t>截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域发力。 公测版APP上线一周的下载量已超1000万。 未来，千问还将陆续接入电商、地图、本地生活等阿里业务生态场景。 在财报电话会上，阿里巴巴高管表示，目前看到客户对AI的需求非常旺盛，阿里云AI服务器上架节奏其实还是严重跟不上客户订单的增长速度，在手积压订单数量还在持续扩大。 8. 中国首个光量子计算机制造工厂！ 从“艺术品”到“工业品”蜕变 据C114报道，11月24日，“国际量子年大湾区活动周”主题活动——</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1704,25 +1704,25 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>行业层面订单与产能回流中国，直接实例</t>
+          <t>泰国工厂案例，与「回流中国」方向相反，仅作同类布局参照</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publisher: 路透社（经环球网 / 新浪转载） Country/Jurisdiction: CN/VN/TH/IN Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用制造 Claim: 部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形</t>
+          <t>截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域发力。 公测版APP上线一周的下载量已超1000万。 未来，千问还将陆续接入电商、地图、本地生活等阿里业务生态场景。 在财报电话会上，阿里巴巴高管表示，目前看到客户对AI的需求非常旺盛，阿里云AI服务器上架节奏其实还是严重跟不上客户订单的增长速度，在手积压订单数量还在持续扩大。 8. 中国首个光量子计算机制造工厂！ 从“艺术品”到“工业品”蜕变 据C114报道，11月24日，“国际量子年大湾区活动周”主题活动——</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>越南扩产以规避关税，服务海外客户的布局案例</t>
+          <t>东南亚建厂以规避与欧美客户合作风险，布局与客户关系直接说明</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一份“炸裂”的半年业绩预告。 数据显示，中际旭创预计上半年实现归母净利润21. 5亿元-25亿元，增长幅度上限超300%，而业绩下限水平甚至已可比肩去年全年。 半年业绩或超去年全年 中际旭创业绩预告显示，该公司预计上半年实现净利润21. 5亿元-25亿元，同比增长250. 3%-307. 33%。 而且，中际旭创还称，今年上半年确认股权激励费用减少公司合并净利润约9300万元。 对于上半年业绩大幅增长，中际旭创解释</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>马来西亚制造—欧美市场的结构，直接说明布局与客户关系</t>
+          <t>马来西亚工厂公开表述为规避地缘风险，直接说明</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>在AI算力基础设施持续扩张的背景下，具备高速率产品量产能力、全球化交付能力与核心器件自研能力的厂商，将在下一阶段竞争中占据主动。 对于下游客户而言，根据自身场景需求在“规模稳定”、“性价比”、“行业定制”三者之间做出选择，已成为当前光模块采购决策的关键。 C114中国通信网版权说明：凡注明来源为“C114通信网”的文章皆属C114版权所有，除与C114签署内容授权协议的单位外，其他单位未经允许禁止转载、摘编，违者必究。 如需使用，请联系021-54451141（汪先生）。 其中编译类仅出于传递更多信息之目的，系C114对海外相关站点最新信息的翻译稿，仅供</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>越南电池基地服务海外客户，布局案例</t>
+          <t>泰国工厂产能与国内齐平，直接说明海外布局</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 / 盖世汽车社区 Country/Jurisdiction: CN/VN Publication date: 2022-11-19 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 与 Vingroup 旗下 VinES 合资（国轩 51% / VinE</t>
+          <t>玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向生产线”的关键一步，也为未来构建自主可控的量子产业链打下了坚实基础。 9. 谷歌TPU硬刚英伟达！ AI芯片市场从英伟达垄断转向多元化 据C114报道，当前全球AI大模型和芯片领域掀起新一轮军备竞赛。 美国白宫周一发布声明称，总统特朗普签署了一项行政命令，启动一项旨在利用AI变革科学研究方式、加速科学发现的全新国家计划“创世纪计划”。 在 AI大模型和芯片竞争背景下，对算力存在巨大需求。 谷歌近日发布了最新的大语</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_005</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>新易盛：2022年设立泰国基地，一二期已投产</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>泰国电池厂配套中国车企在泰车型，布局与客户关系直接</t>
+          <t>泰国基地服务海外客户，直接说明布局与客户关系</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向生产线”的关键一步，也为未来构建自主可控的量子产业链打下了坚实基础。 9. 谷歌TPU硬刚英伟达！ AI芯片市场从英伟达垄断转向多元化 据C114报道，当前全球AI大模型和芯片领域掀起新一轮军备竞赛。 美国白宫周一发布声明称，总统特朗普签署了一项行政命令，启动一项旨在利用AI变革科学研究方式、加速科学发现的全新国家计划“创世纪计划”。 在 AI大模型和芯片竞争背景下，对算力存在巨大需求。 谷歌近日发布了最新的大语</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>回流案例，说明海外布局风险，但非“东南亚扩产服务欧美客户”的直接说明</t>
+          <t>泰国一期投产、二期在建，直接说明海外布局</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向生产线”的关键一步，也为未来构建自主可控的量子产业链打下了坚实基础。 9. 谷歌TPU硬刚英伟达！ AI芯片市场从英伟达垄断转向多元化 据C114报道，当前全球AI大模型和芯片领域掀起新一轮军备竞赛。 美国白宫周一发布声明称，总统特朗普签署了一项行政命令，启动一项旨在利用AI变革科学研究方式、加速科学发现的全新国家计划“创世纪计划”。 在 AI大模型和芯片竞争背景下，对算力存在巨大需求。 谷歌近日发布了最新的大语</t>
         </is>
       </c>
     </row>
@@ -2378,44 +2378,44 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>越南消费电池建厂案例，与规避认定无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>白宫点名东南亚转运高风险并推AI执法，直接说明认定规避的官方立场</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>终止海外项目案例，与规避认定无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>印度订单回流案例，与规避/未规避认定无关 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -4149,17 +4149,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4168,25 +4168,25 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>终止马来西亚项目，与该假设无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>官方执法立场，说明原产地改判风险</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -4226,44 +4226,44 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>欧洲业务收缩，与该假设无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>中间品出口数据，可作原产地认定背景，非执法判例本身</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4303,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>官方执法立场，说明原产地改判风险</t>
+          <t>白宫非法转运报告，官方执法立场直接证据</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -4380,44 +4380,44 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>越南建厂案例，不提供执法判断 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>EO14411 加强海关执法，直接回答执法趋势 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -4534,17 +4534,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4553,25 +4553,25 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>企业终止海外项目案例，可作立项风险的实例参考，但非制度/环境证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>中国对外投资官方规则，直接</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>中国对外投资官方规则，直接</t>
+          <t>世界投资报告，国际投资环境直接证据</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -4688,44 +4688,44 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>企业终止欧洲业务，同为企业层面立项参考 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>全球风险报告，宏观风险框架，非投资制度/环境证据</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research Assistant Benin Institut de Recherche Empirique en Economie Politique - IREEP Leonard Wantchekon, President Stéphania Houngan, Research Associate Bolivia (Plurinational State of), Costa Rica, Dominican Republi</t>
         </is>
       </c>
     </row>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>企业海外建厂案例，同为企业层面立项参考 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>企业放弃海外建厂个案，可作立项风险实例，非制度/环境证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -5073,22 +5073,22 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
@@ -5098,19 +5098,19 @@
         <v>2</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>企业个案，与碎片化趋势判断无关</t>
+          <t>UN Comtrade 贸易流数据，可作碎片化趋势间接佐证，非投资判断证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_001 Title: 恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） Publisher: 恩捷股份公告（经东方财富网 / 央广网报道） Country/Jurisdiction: CN/MY Publication date: 2026-05-22 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电池材料 Claim: 2026</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>企业建厂案例，与趋势判断无关</t>
+          <t>企业个案，与地缘经济碎片化趋势判断无关</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
         </is>
       </c>
     </row>
@@ -5304,44 +5304,44 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增））</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>企业欧洲布局收缩，可作不确定性的具体例证，但非高权威全球证据</t>
+          <t>FDI与地缘经济碎片化框架，直接</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
     </row>
@@ -5381,17 +5381,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>FDI与地缘经济碎片化框架，直接</t>
+          <t>货物贸易增速放缓，直接</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
     </row>
@@ -5458,44 +5458,44 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>企业终止海外项目，同为例证，非宏观证据</t>
+          <t>全球风险报告将地缘经济对抗列为首要风险，直接支撑判断</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
     </row>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>The art, science, and technology of geopolitical scenario planning</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>货物贸易增速放缓，直接</t>
+          <t>地缘政治情景规划方法，直接支撑海外布局不确定性分析</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
         </is>
       </c>
     </row>
@@ -6459,44 +6459,44 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>泰国电池厂案例，佐证产能转移，非贸易数据</t>
+          <t>中国对越/泰/马中间品出口，直接</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -6536,44 +6536,44 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>越南电池厂案例，佐证产能转移</t>
+          <t>白宫非法转运报告，供应链迁移相关政策证据直接来源 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -6613,44 +6613,44 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>马来西亚电池厂案例，佐证产能转移</t>
+          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
     </row>
@@ -6690,44 +6690,44 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>中国对越/泰/马中间品出口，直接</t>
+          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -6921,44 +6921,44 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>欣旺达越南基地：越南建厂但仍依赖中国材料，依赖例证</t>
+          <t>非法转运报告，原产地风险直接</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -6998,44 +6998,44 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>国轩高科越南基地：正负极材料仍来自中国，依赖例证</t>
+          <t>全球贸易展望，提供背景但非中间品依赖/原产地风险的直接证据</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
+          <t>35 Appendix Table 1: Leading exporters and importers in world merchandise trade, 2025 (Billion dollars and percentage) Rank Exporters Value Share Annual percentage change Rank Importers Value Share Annual percentage change 1 China 3,772 14. 4 5 1 United States of America 3,507 13</t>
         </is>
       </c>
     </row>
@@ -7075,12 +7075,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>非法转运报告，原产地风险直接</t>
+          <t>转运可见性分析，直接支持原产地风险判断</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -7152,44 +7152,44 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>越南仅承担电芯制造、材料仍由中国供应，支持“未隔离风险”</t>
+          <t>中国对东南亚中间品出口数据，直接支撑「依赖未隔离」判断</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -7229,44 +7229,44 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>泰国仅承担模组PACK、电芯材料仍从中国输入，直接支持</t>
+          <t>反规避「认定规避」，直接支撑风险未隔离</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -7306,12 +7306,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7325,25 +7325,25 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>材料仍由中国输入，例证</t>
+          <t>东南亚建厂规避欧美客户风险，直接案例</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publisher: 新浪财经 Country/Jurisdiction: CN/MY Publication date: 2026-02-06 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/储能 Claim: 在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
     </row>
@@ -7383,22 +7383,22 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>零部件本地化仍在爬坡、依赖中泰跨境供应，例证</t>
+          <t>美国进口贸易数据，可作布局结果佐证，非风险隔离证据</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ##</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
     </row>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>终止海外项目、对单一中国基地依赖上升，直接说明风险未隔离</t>
+          <t>订单转移印度后回流，直接说明海外迁移未达预期</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7537,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>1</v>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>欣旺达越南扩产，供应链布局调整的直接案例 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>订单回流、放弃海外建厂，直接说明布局调整与执行风险</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>KPMG_001</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>KPMG 2026 US Supply Chain Survey</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7629,11 +7629,11 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>2</v>
@@ -7646,12 +7646,12 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>终止海外项目、资源回投国内，直接说明执行风险 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>KPMG供应链调查，直接提供企业执行风险证据</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>毕马威（KPMG）</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher: 毕马威（KPMG） Country/Jurisdiction: US / Federal Publication date: 2026-05-01 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用 Key finding: 样本为462位年营收10亿美元以上企业的供应链负责人。样本是美国大企业，不代表</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>1</v>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能马来西亚投产，布局调整案例 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>东南亚建厂规避客户风险，直接说明布局调整</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7783,29 +7783,29 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>比亚迪泰国投产，布局调整案例</t>
+          <t>泰国工厂产能齐平，直接说明布局调整</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_001 Title: 比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网（转比亚迪官方） Country/Jurisdiction: CN/TH Publication date: 2024-07-04 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 整车/汽车 Claim: 2022-09 与 WHA 签约，在泰国罗勇府建全资乘用车工厂；2024-07-04 竣工投产，年</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
     </row>
@@ -7845,44 +7845,44 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：China + 1 战略（多地区混合布局）</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>CATL 匈牙利 China+1，布局调整案例</t>
+          <t>反规避判例，属监管风险证据，非供应链韧性/执行风险主体 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: PLUS1_001 Title: 宁德时代 CATL：China + 1 战略（多地区混合布局） Publisher: 每日经济新闻 / 搜狐网 Country/Jurisdiction: CN/HU Publication date: 2026-09-22 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在匈牙利德布勒森建设欧洲第二座电池工厂，投资约 73.4 亿欧元（匈牙利史上最大外资项目之一）</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -8153,17 +8153,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -8178,19 +8178,19 @@
         <v>2</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>企业终止海外项目，与地理集中评估弱相关</t>
+          <t>海关执法行政令，对应非法转运审查维度 ｜ 人工判定与Auto(1)不同，请复核 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -8230,22 +8230,22 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
@@ -8255,19 +8255,19 @@
         <v>2</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>海关执法行政令，对应非法转运审查维度 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>全球贸易展望，提供宏观背景，非集中度/转运审查直接证据</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
         </is>
       </c>
     </row>
@@ -8923,17 +8923,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>企业回流案例，与受限方筛查无关</t>
+          <t>反规避「未规避」判例，与限制清单筛查无关</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -9000,44 +9000,44 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>企业建厂案例，与受限方筛查无关</t>
+          <t>中国两用物项目录，属清单类证据，但为中国口径非美方限制清单</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>-154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门设计或制造的激 光器或激光系统。 在以激光为基础的浓缩过程中有重要 意义的激光器和激光部件包括《中华人 民共和国两用物项出口管制清单》中所 列的那些激光器和激光部件。激光系统 一般包含用于管理激光束（一个或多 个）和向同位素分离室发射激光束的光 学和电子部件。AVLIS 过程使用的激 光系统通常由两个激光器组成：一个铜 蒸气激光器或某些固体激光器和一个 可调染料激光器。MLIS使用的激光系 统通常由一个 CO2激</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
@@ -9693,44 +9693,44 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>越南建厂案例，机会侧间接佐证 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>转运可见性分析，直接支撑美国强化转运执法的风险判断</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华加征关税及客户'中国+1'采购要求，推动消费类电芯产线外移。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威消费类锂电池工厂项目，投资总额不超过 20 亿元人民币；2026-08 公司表示越南消费类电芯生产基地预计 2026 年底投产。中国产能保留。 ## 四、相关风险（Related Risk） 风险</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>泰国建厂案例，机会侧间接佐证 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>东南亚建厂规避客户风险，直接说明市场准入机会</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ##</t>
+          <t>中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一份“炸裂”的半年业绩预告。 数据显示，中际旭创预计上半年实现归母净利润21. 5亿元-25亿元，增长幅度上限超300%，而业绩下限水平甚至已可比肩去年全年。 半年业绩或超去年全年 中际旭创业绩预告显示，该公司预计上半年实现净利润21. 5亿元-25亿元，同比增长250. 3%-307. 33%。 而且，中际旭创还称，今年上半年确认股权激励费用减少公司合并净利润约9300万元。 对于上半年业绩大幅增长，中际旭创解释</t>
         </is>
       </c>
     </row>
@@ -10463,44 +10463,44 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>跟踪情景走向的官方监测入口</t>
+          <t>金属铸造回流案例，与BIS规则情景无关</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -10540,44 +10540,44 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>金属铸造回流案例，与BIS规则情景无关</t>
+          <t>跟踪情景走向的官方监测入口</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>转运执法证据，题目点名要求 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>转运执法证据，题目点名要求 ｜ 人工判定与Auto(1)不同，请复核 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>反规避终裁，界定“实质性转变”，直接 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>反规避终裁，界定“实质性转变”，直接 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -11310,17 +11310,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -11329,25 +11329,25 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>企业终止海外项目，与两种采购方案比较弱相关</t>
+          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -11464,17 +11464,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -11483,25 +11483,25 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J143" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>全球投资趋势，直接</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -11541,17 +11541,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -11560,25 +11560,25 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J144" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>全球投资趋势，直接</t>
+          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
     </row>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>企业终止海外项目案例，非题目所问的三类证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>企业放弃海外建厂个案，可作延后投资决策参考，非投资政策/趋势证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
@@ -11926,17 +11926,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例）</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -11951,19 +11951,19 @@
         <v>2</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J149" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>企业退出海外布局，说明集中布局风险，间接相关</t>
+          <t>海关执法，对应准入风险 ｜ 人工判定与Auto(1)不同，请复核 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -12003,44 +12003,44 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>泰国电池厂案例，直接支持泰国单一中心方案</t>
+          <t>美国自中/越/泰/马进口贸易数据，直接支撑集中度与准入比较</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
     </row>
@@ -12080,44 +12080,44 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>海关执法，对应准入风险 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>马来西亚工厂案例，直接支撑泰马分散布局情景</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18. 81亿-21. 50亿元，净利率高达37. 40%，盈利质量行业领先。 公司1. 6T光引擎实现规模化量产，布局CPO无源器件，深度绑定中际旭创、新易盛等头部厂商。 作为“卖铲人”定位，天孚通信在技术迭代中具备更强的抗风险能力。 三、第三梯队 7. 剑桥科技 剑桥科技2025年预计归母净利润2. 52亿-2. 78亿元，同比增长51%-67%。 800G LPO光模块通过客户验证，1. 6T产品进入Meta供应</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A2,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>泰国扩产案例充足，且新增回流案例可作节奏反向参照</t>
+          <t>泰国产能案例（CASE_004/005/006/008）全部命中，可直接回答建厂节奏</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_003; RELOC_002; RELOC_001</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A3,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>马来西亚布局案例（含电池链）+ 美国官方转运判断均已覆盖</t>
+          <t>马来西亚布局案例与美方对马来西亚原产地的官方判断均已覆盖（CASE_008未命中，由CASE_007/CASE_003/CASE_002覆盖）</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_010</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A4,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12371,11 +12371,11 @@
         <v/>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>回流/撤出案例充足；RETURN_002 因「回流」未证实记为部分相关，不影响覆盖</t>
+          <t>仅 CASE_001 为直接的「回流并放弃海外建厂」实例，其余4条为东南亚扩厂案例，方向相反</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -12395,12 +12395,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A5,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>东南亚电池链布局案例齐全，客户/地缘关联明确</t>
+          <t>gold 五条全部命中，布局与客户/地缘关系全覆盖</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_004; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A6,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>规避/未规避双向判例 + 官方终裁齐全</t>
+          <t>「认定规避」与「未规避」双向判例 + 官方立场齐全</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001</t>
         </is>
       </c>
     </row>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>中国目录与暂停 + 美方穿透规则齐全</t>
+          <t>美方穿透规则与中方目录/暂停措施齐全</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>暂停期与恢复时点齐全，可直接判断窗口</t>
+          <t>暂停期与恢复规则齐全；FR_001未命中但由BIS_001/002覆盖</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>政策方向 + 执法先例齐全</t>
+          <t>政策方向、行政令与执法先例齐全</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A11,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12749,11 +12749,11 @@
         <v/>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>判例仅命中2条（CASE_002/CASE_010），第2/3名案例证据与该假设无关</t>
+          <t>「认定规避」判例与美方执法立场齐全（CASE_003/DOC_001未命中，由CASE_002/WH_002替代）</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005</t>
+          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12792,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A12,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12803,11 +12803,11 @@
         <v/>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>仅命中中国规则与IMF证据，缺UNCTAD国际投资趋势</t>
+          <t>中国官方规则 + IMF/UNCTAD 国际投资环境证据齐全</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; RETURN_001; CNGOV_001; RETURN_004; RELOC_004</t>
+          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>仅WEF+UNCTAD命中，缺IMF碎片化框架与麦肯锡情景证据</t>
+          <t>仅 WEF/UNCTAD 命中，缺 IMF 碎片化框架与麦肯锡情景证据</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A14,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12915,7 +12915,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>贸易、投资、风险三类高权威证据基本齐全</t>
+          <t>贸易、投资、风险三类高权威证据齐全</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; RETURN_004; IMF_001; RETURN_001; WTO_001</t>
+          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001</t>
         </is>
       </c>
     </row>
@@ -13073,11 +13073,11 @@
         <v/>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>贸易数据两侧齐全，但缺政策侧证据（CASE_010未命中）</t>
+          <t>贸易数据两侧 + 政策侧证据齐全</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; RELOC_004; TRD_003</t>
+          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A18,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13170,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A19,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13181,11 +13181,11 @@
         <v/>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>案例侧仅命中RELOC_005/006/004/002/RETURN_001，缺中间品数据与反规避判例</t>
+          <t>案例与贸易数据充足；CASE_003未命中但CASE_002覆盖原产地认定</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_006; RELOC_004; RELOC_002; RETURN_001</t>
+          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A20,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13235,11 +13235,11 @@
         <v/>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>企业案例齐全，但缺供应链调查证据（KPMG_001未命中）</t>
+          <t>企业案例 + KPMG供应链调查齐全</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RETURN_001; RELOC_004; RELOC_001; PLUS1_001</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003</t>
         </is>
       </c>
     </row>
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>依赖数据 + 执法证据 + 企业案例齐全</t>
+          <t>中间品依赖与转运审查证据齐全；CSIS_001未命中由WH_002/CASE_010覆盖</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_001; WH_001</t>
+          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>执法证据齐全，足以否定“仅凭申报原产地”</t>
+          <t>执法证据齐全，足以否定「仅凭申报原产地」</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -13397,11 +13397,11 @@
         <v/>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>缺受限方筛查数据源（ITA_001未命中）</t>
+          <t>受限方筛查数据源与规则齐全（BIS_001/002 + CASE_009 + ITA_001）</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; RETURN_001; RELOC_006</t>
+          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A25,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; RELOC_005; RELOC_002</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>两种情景均有直接依据</t>
+          <t>两种情景均有直接依据（ITA_001未命中由BIS_001/002覆盖）</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; CASE_001</t>
+          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A29,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -13775,11 +13775,11 @@
         <v/>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>投资政策与全球趋势齐全，企业调查证据缺失但可接受</t>
+          <t>缺企业供应链调查证据（KPMG_001）与麦肯锡情景证据</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; UNCTAD_001; CNGOV_001; RETURN_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A31,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13833,7 +13833,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>案例与执法证据齐全，但缺贸易数据侧（TRD_001未命中）</t>
+          <t>贸易数据与执法证据齐全，但泰国产能案例（CASE_004/005/006）未命中，情景A支撑不足</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RETURN_001; RELOC_006; WH_001</t>
+          <t>CASE_010; WH_002; WH_001; TRD_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AI-assisted pre-scoring (content-based). Review flagged rows before finalising.</t>
+          <t>AI-assisted pre-scoring (content-based, keyed by evidence_id). Review flagged rows before finalising.</t>
         </is>
       </c>
     </row>

--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -1608,12 +1608,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50%穿透规则原文，直接回答美方规则</t>
+          <t>暂停令，直接回答暂停措施</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>暂停令，直接回答暂停措施</t>
+          <t>50%穿透规则原文，直接回答美方规则</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2705,25 +2705,25 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>中国两用物项目录，直接回答核查范围</t>
+          <t>BIS规则时间线合成案例，内容重复BIS_001/002</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、海关总署 Country/Jurisdiction: CN / National Publication date: 2025-12-31 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 2026-01-01起实施，同时废止2024年第67号公告。用于判断产品是否属于中国侧</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2782,25 +2782,25 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>BIS规则时间线合成案例，内容重复BIS_001/002</t>
+          <t>暂停措施涉及镓、锗、石墨，直接回答</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2840,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>暂停措施涉及镓、锗、石墨，直接回答</t>
+          <t>中国两用物项目录，直接回答核查范围</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、海关总署 Country/Jurisdiction: CN / National Publication date: 2025-12-31 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 2026-01-01起实施，同时废止2024年第67号公告。用于判断产品是否属于中国侧</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>50%持股穿透规则原文</t>
+          <t>暂停期原文，直接回答时间判断</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>暂停期原文，直接回答时间判断</t>
+          <t>50%持股穿透规则原文</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单）</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>筛查数据源，对窗口风险为辅助</t>
+          <t>中国侧暂停措施，机制不同，仅辅助</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -3610,17 +3610,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3629,25 +3629,25 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>中国侧暂停措施，机制不同，仅辅助</t>
+          <t>本题 expected 证据：美国联邦公报是 BIS 关联企业规则发布/暂停/恢复的官方可追溯渠道</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>白宫转运报告，政策方向直接证据</t>
+          <t>点名越/泰/马为转运高风险，直接</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>点名越/泰/马为转运高风险，直接</t>
+          <t>白宫转运报告，政策方向直接证据</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -4226,22 +4226,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -4251,19 +4251,19 @@
         <v>2</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>中间品出口数据，可作原产地认定背景，非执法判例本身</t>
+          <t>EO14411 加强海关执法，直接回答执法趋势 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -4380,44 +4380,44 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>EO14411 加强海关执法，直接回答执法趋势 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>订单转移海外后回流的企业案例，可佐证‘海外加工未必改变原产地定性与救济结果’，但非原产地认定执法案例</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>地缘经济碎片化框架，国际投资环境证据，直接</t>
+          <t>中国对外投资官方规则，直接</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>中国对外投资官方规则，直接</t>
+          <t>地缘经济碎片化框架，国际投资环境证据，直接</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
     </row>
@@ -4688,44 +4688,44 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>全球风险报告，宏观风险框架，非投资制度/环境证据</t>
+          <t>企业放弃海外建厂个案，可作立项风险实例，非制度/环境证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research Assistant Benin Institut de Recherche Empirique en Economie Politique - IREEP Leonard Wantchekon, President Stéphania Houngan, Research Associate Bolivia (Plurinational State of), Costa Rica, Dominican Republi</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -4765,44 +4765,44 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>The art, science, and technology of geopolitical scenario planning</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>企业放弃海外建厂个案，可作立项风险实例，非制度/环境证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>地缘情景规划方法论，可作为海外投资立项的风险评估框架，属支持性证据</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Once leaders have defined their objectives, they can choose from a tool kit of foresight development instruments. Below, we outline five that organizations frequently employ: — Horizon scanning: gathering internal and external perspectives to create a baseline understanding of th</t>
         </is>
       </c>
     </row>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>全球投资与地缘经济趋势，直接</t>
+          <t>FDI与地缘经济碎片化框架，直接</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>FDI与地缘经济碎片化框架，直接</t>
+          <t>全球投资与地缘经济趋势，直接</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>The art, science, and technology of geopolitical scenario planning</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>全球风险报告将地缘经济对抗列为首要风险，直接支撑判断</t>
+          <t>地缘政治情景规划方法，直接支撑海外布局不确定性分析</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
         </is>
       </c>
     </row>
@@ -5535,12 +5535,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>地缘政治情景规划方法，直接支撑海外布局不确定性分析</t>
+          <t>全球风险报告将地缘经济对抗列为首要风险，直接支撑判断</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
     </row>
@@ -6459,44 +6459,44 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>中国对越/泰/马中间品出口，直接</t>
+          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -6536,22 +6536,22 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
@@ -6561,19 +6561,19 @@
         <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>白宫非法转运报告，供应链迁移相关政策证据直接来源 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6632,20 +6632,20 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
+          <t>中国对越/泰/马中间品出口，直接</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -6690,17 +6690,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -6709,25 +6709,25 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>白宫非法转运报告，供应链迁移相关政策证据直接来源 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -6998,44 +6998,44 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，提供背景但非中间品依赖/原产地风险的直接证据</t>
+          <t>转运可见性分析，直接支持原产地风险判断</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>35 Appendix Table 1: Leading exporters and importers in world merchandise trade, 2025 (Billion dollars and percentage) Rank Exporters Value Share Annual percentage change Rank Importers Value Share Annual percentage change 1 China 3,772 14. 4 5 1 United States of America 3,507 13</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -7075,12 +7075,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>转运可见性分析，直接支持原产地风险判断</t>
+          <t>加强海关执法行政令，涉及原产地核查，是原产地风险的执法背景，但未直接讨论中间品依赖</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -7152,22 +7152,22 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>中国对东南亚中间品出口数据，直接支撑「依赖未隔离」判断</t>
+          <t>反规避「认定规避」，直接支撑风险未隔离</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -7229,22 +7229,22 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>反规避「认定规避」，直接支撑风险未隔离</t>
+          <t>中国对东南亚中间品出口数据，直接支撑「依赖未隔离」判断</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -7383,44 +7383,44 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>美国进口贸易数据，可作布局结果佐证，非风险隔离证据</t>
+          <t>订单转移印度后回流，直接说明海外迁移未达预期</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -7460,44 +7460,44 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>订单转移印度后回流，直接说明海外迁移未达预期</t>
+          <t>美国进口贸易数据，可作布局结果佐证，非风险隔离证据</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
     </row>
@@ -7768,44 +7768,44 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>泰国工厂产能齐平，直接说明布局调整</t>
+          <t>反规避判例，属监管风险证据，非供应链韧性/执行风险主体 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -7845,44 +7845,44 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>反规避判例，属监管风险证据，非供应链韧性/执行风险主体 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>泰国工厂产能齐平，直接说明布局调整</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>转运审查，直接</t>
+          <t>点名泰/马转运高风险，直接</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
         </is>
       </c>
     </row>
@@ -8076,12 +8076,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>点名泰/马转运高风险，直接</t>
+          <t>转运审查，直接</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -8230,44 +8230,44 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，提供宏观背景，非集中度/转运审查直接证据</t>
+          <t>本题 expected 证据：USMCA 下中国转运可视化与执法分析</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -8923,17 +8923,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，与限制清单筛查无关</t>
+          <t>欧盟电池法规属欧盟市场准入要求，与‘客户被美国限制清单覆盖’的受限方筛查问题无关，属跨辖区噪声</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
         </is>
       </c>
     </row>
@@ -9000,17 +9000,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>2</v>
@@ -9032,12 +9032,12 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>中国两用物项目录，属清单类证据，但为中国口径非美方限制清单</t>
+          <t>FEOC 规则以‘外国关注实体’认定电池组件/关键矿物准入资格，可支持美国市场准入风险判断，但不针对客户限制清单筛查 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>-154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门设计或制造的激 光器或激光系统。 在以激光为基础的浓缩过程中有重要 意义的激光器和激光部件包括《中华人 民共和国两用物项出口管制清单》中所 列的那些激光器和激光部件。激光系统 一般包含用于管理激光束（一个或多 个）和向同位素分离室发射激光束的光 学和电子部件。AVLIS 过程使用的激 光系统通常由两个激光器组成：一个铜 蒸气激光器或某些固体激光器和一个 可调染料激光器。MLIS使用的激光系 统通常由一个 CO2激</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
     </row>
@@ -9077,12 +9077,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>官方反规避终裁原文，直接</t>
+          <t>“认定规避”判例，直接</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9154,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>“认定规避”判例，直接</t>
+          <t>官方反规避终裁原文，直接</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
     </row>
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -9340,12 +9340,12 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>转运执法，直接</t>
+          <t>东南亚转运高风险，直接</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
         </is>
       </c>
     </row>
@@ -9385,12 +9385,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>东南亚转运高风险，直接</t>
+          <t>转运执法，直接</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -10078,12 +10078,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>The art, science, and technology of geopolitical scenario planning</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>首要风险与不确定性，直接</t>
+          <t>地缘政治情景规划，直接</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
         </is>
       </c>
     </row>
@@ -10155,44 +10155,44 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>地缘政治情景规划，直接</t>
+          <t>中国境内对外投资管理规定，不反映全球需求与投资环境，与本题宏观证据需求无关</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
     </row>
@@ -10309,12 +10309,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>情景A（规则恢复）的直接依据</t>
+          <t>完整时间线，直接</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
     </row>
@@ -10386,12 +10386,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>完整时间线，直接</t>
+          <t>情景A（规则恢复）的直接依据</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
         </is>
       </c>
     </row>
@@ -10463,44 +10463,44 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>金属铸造回流案例，与BIS规则情景无关</t>
+          <t>跟踪情景走向的官方监测入口</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
     </row>
@@ -10540,44 +10540,44 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>跟踪情景走向的官方监测入口</t>
+          <t>金属铸造回流案例，与BIS规则情景无关</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>终裁原文，直接</t>
+          <t>“认定规避”判例，直接</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>“认定规避”判例，直接</t>
+          <t>终裁原文，直接</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
     </row>
@@ -11079,17 +11079,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>转运与原产地风险，直接</t>
+          <t>“认定规避”判例，直接</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -11156,12 +11156,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>2</v>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>反规避终裁，界定“实质性转变”，直接 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
     </row>
@@ -11233,17 +11233,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>“认定规避”判例，直接</t>
+          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -11310,17 +11310,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
+          <t>转运与原产地风险，直接</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -11464,17 +11464,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -11483,25 +11483,25 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J143" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>全球投资趋势，直接</t>
+          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
     </row>
@@ -11541,44 +11541,44 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J144" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>中国对外投资规则，直接</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
     </row>
@@ -11618,12 +11618,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>中国对外投资规则，直接</t>
+          <t>全球投资趋势，直接</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -11695,44 +11695,44 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例）</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>企业放弃海外建厂个案，可作延后投资决策参考，非投资政策/趋势证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>欧盟外资安全审查框架，属‘投资政策’证据，可用于评估海外建厂面临的东道国审查风险</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2019-03-21 Effective da</t>
         </is>
       </c>
     </row>
@@ -12003,44 +12003,44 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>美国自中/越/泰/马进口贸易数据，直接支撑集中度与准入比较</t>
+          <t>马来西亚/越南被认定‘未规避’的企业对照案例，可为‘泰国 vs 泰马分散’的市场准入比较提供参考，但属光伏行业类比 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A9,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001</t>
         </is>
       </c>
     </row>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001</t>
+          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003</t>
+          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001</t>
+          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A21,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001</t>
+          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A26,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A29,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003</t>
+          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001</t>
+          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A31,'Item Scoring'!$I$2:$I$151),"")</f>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_001; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_007</t>
         </is>
       </c>
     </row>

--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Rubric" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Scoring'!$A$1:$Q$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Scoring'!$A$1:$Q$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2378,17 +2378,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2397,25 +2397,25 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚转运高风险并推AI执法，直接说明认定规避的官方立场</t>
+          <t>UFLPA 强迫劳动实体清单，与反规避/原产地认定判例属不同域</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -2455,44 +2455,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>印度订单回流案例，与规避/未规避认定无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>白宫点名东南亚转运高风险并推AI执法，直接说明认定规避的官方立场</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>暂停期原文，直接回答时间判断</t>
+          <t>50%持股穿透规则原文</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50%持股穿透规则原文</t>
+          <t>暂停期原文，直接回答时间判断</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
     </row>
@@ -3225,17 +3225,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3244,25 +3244,25 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>新规监测入口，非穿透判断本身</t>
+          <t>UFLPA 清单不是 Entity List/MEU 穿透规则，与 50% 持股判断无关</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -3610,17 +3610,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3629,25 +3629,25 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：美国联邦公报是 BIS 关联企业规则发布/暂停/恢复的官方可追溯渠道</t>
+          <t>企业年报披露半导体出口管制风险，不涉及关联企业规则暂停/恢复时间线 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -4245,25 +4245,25 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>EO14411 加强海关执法，直接回答执法趋势 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>强迫劳动清单与‘东南亚加工能否改变原产地’无关</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4303,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>2</v>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>白宫非法转运报告，官方执法立场直接证据</t>
+          <t>EO14411 加强海关执法，直接回答执法趋势 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -4380,44 +4380,44 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>订单转移海外后回流的企业案例，可佐证‘海外加工未必改变原产地定性与救济结果’，但非原产地认定执法案例</t>
+          <t>白宫非法转运报告，官方执法立场直接证据</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -4765,44 +4765,44 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>地缘情景规划方法论，可作为海外投资立项的风险评估框架，属支持性证据</t>
+          <t>既非中国对外投资规则，也非国际投资环境证据</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Once leaders have defined their objectives, they can choose from a tool kit of foresight development instruments. Below, we outline five that organizations frequently employ: — Horizon scanning: gathering internal and external perspectives to create a baseline understanding of th</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -4842,17 +4842,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4861,25 +4861,25 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>地缘经济对抗列为首要风险，直接</t>
+          <t>WTO 对印贸易政策审议属官方贸易政策环境证据，可用作碎片化的国别佐证，但非国际组织宏观/投资证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
         </is>
       </c>
     </row>
@@ -4919,17 +4919,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>动荡期FDI趋势，直接</t>
+          <t>地缘经济对抗列为首要风险，直接</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5011,29 +5011,29 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>中国国内规定，非国际组织证据</t>
+          <t>动荡期FDI趋势，直接</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
         </is>
       </c>
     </row>
@@ -5073,26 +5073,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>2</v>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>UN Comtrade 贸易流数据，可作碎片化趋势间接佐证，非投资判断证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>中国国内规定，非国际组织证据</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
     </row>
@@ -5150,44 +5150,44 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>企业个案，与地缘经济碎片化趋势判断无关</t>
+          <t>WTO 对印尼贸易政策审议，同上：国别贸易政策环境证据，非全球宏观趋势证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
+          <t>122 Indonesia Investments, Holding Company for Indonesia's State-Owned Miners Ready in Q1-2017. Viewed at: https://www. indonesia-investments. com/news/todays-headlines/holding-company-for-indonesia-s- state-owned-miners-ready-in-q1-2017/item7541; and Deloitte, 2019-20 Investment</t>
         </is>
       </c>
     </row>
@@ -5920,17 +5920,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -5945,19 +5945,19 @@
         <v>2</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>新规监测入口，非名称筛查数据源</t>
+          <t>企业年报披露，不是受限方筛查数据源，也不构成出口管制规则 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key</t>
         </is>
       </c>
     </row>
@@ -6459,44 +6459,44 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>中国对越/泰/马中间品出口，直接</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -6536,26 +6536,26 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>2</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
+          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6632,20 +6632,20 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>中国对越/泰/马中间品出口，直接</t>
+          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
     </row>
@@ -6690,17 +6690,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -6709,25 +6709,25 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>白宫非法转运报告，供应链迁移相关政策证据直接来源 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>强迫劳动清单不能支持美国 EV/电池进口来源是否转移的判断</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -7075,22 +7075,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>加强海关执法行政令，涉及原产地核查，是原产地风险的执法背景，但未直接讨论中间品依赖</t>
+          <t>全球贸易展望，提供背景但非中间品依赖/原产地风险的直接证据</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>35 Appendix Table 1: Leading exporters and importers in world merchandise trade, 2025 (Billion dollars and percentage) Rank Exporters Value Share Annual percentage change Rank Importers Value Share Annual percentage change 1 China 3,772 14. 4 5 1 United States of America 3,507 13</t>
         </is>
       </c>
     </row>
@@ -7383,44 +7383,44 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>订单转移印度后回流，直接说明海外迁移未达预期</t>
+          <t>不涉及产能布局与供应链依赖，与‘外移最终环节能否隔离风险’无关</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7706,29 +7706,29 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>东南亚建厂规避客户风险，直接说明布局调整</t>
+          <t>全球电池装车量与厂商份额，可佐证头部企业供给格局，但不涉及企业布局调整与扩产执行风险</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
         </is>
       </c>
     </row>
@@ -7845,12 +7845,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>泰国工厂产能齐平，直接说明布局调整</t>
+          <t>东南亚建厂规避客户风险，直接说明布局调整</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>点名泰/马转运高风险，直接</t>
+          <t>转运审查，直接</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -8076,12 +8076,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>转运审查，直接</t>
+          <t>本题 expected 证据：USMCA 下中国转运可视化与执法分析</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -8153,26 +8153,26 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>2</v>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>海关执法行政令，对应非法转运审查维度 ｜ 人工判定与Auto(1)不同，请复核 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>本题 expected 证据：美国自中/越/泰/马进口 EV 与锂电池数据，直接支撑地理集中度评估</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
     </row>
@@ -8230,44 +8230,44 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：USMCA 下中国转运可视化与执法分析</t>
+          <t>全球贸易展望，提供宏观背景，非集中度/转运审查直接证据</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -8557,25 +8557,25 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J105" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>EO14411进口商问责，直接</t>
+          <t>USMCA 原产地成分门槛可作为‘原产地需实质举证’的同类规则参照，但本题聚焦美方对东南亚转运与原产地的执法</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
         </is>
       </c>
     </row>
@@ -8615,17 +8615,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>仅凭申报原产地仍被认定中国原产，直接</t>
+          <t>EO14411进口商问责，直接</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -8923,17 +8923,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>欧盟电池法规属欧盟市场准入要求，与‘客户被美国限制清单覆盖’的受限方筛查问题无关，属跨辖区噪声</t>
+          <t>UFLPA 清单不是美国出口管制受限方清单，与受限方筛查流程无关</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -9000,17 +9000,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -9025,19 +9025,19 @@
         <v>2</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>FEOC 规则以‘外国关注实体’认定电池组件/关键矿物准入资格，可支持美国市场准入风险判断，但不针对客户限制清单筛查 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>欧盟电池法规属欧盟市场准入要求，与‘客户被美国限制清单覆盖’的受限方筛查问题无关，属跨辖区噪声</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
         </is>
       </c>
     </row>
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -9340,12 +9340,12 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>东南亚转运高风险，直接</t>
+          <t>转运执法，直接</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -9385,12 +9385,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>转运执法，直接</t>
+          <t>东南亚转运高风险，直接</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
         </is>
       </c>
     </row>
@@ -10078,44 +10078,44 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>地缘政治情景规划，直接</t>
+          <t>WTO 对印贸易政策审议可作国别贸易政策环境证据，但非全球宏观需求/投资环境证据</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
+          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
         </is>
       </c>
     </row>
@@ -10155,44 +10155,44 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WTO_003</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度）</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>中国境内对外投资管理规定，不反映全球需求与投资环境，与本题宏观证据需求无关</t>
+          <t>WTO 印度关税快照可作国别准入环境数据，但非全球宏观趋势证据</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2025-07 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: WTO国别</t>
         </is>
       </c>
     </row>
@@ -10463,44 +10463,44 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>跟踪情景走向的官方监测入口</t>
+          <t>金属铸造回流案例，与BIS规则情景无关</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -10540,44 +10540,44 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>金属铸造回流案例，与BIS规则情景无关</t>
+          <t>跟踪情景走向的官方监测入口</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10848,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>2</v>
@@ -10880,12 +10880,12 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>转运执法证据，题目点名要求 ｜ 人工判定与Auto(1)不同，请复核 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>转运执法证据，题目点名要求</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -10925,44 +10925,44 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J136" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>转运执法证据，题目点名要求</t>
+          <t>中国对东南亚中间品出口数据，可佐证‘迁移工序≠切断中间品依赖’，但本题核心是反规避/转运判例</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
     </row>
@@ -11156,17 +11156,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -11188,12 +11188,12 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
+          <t>转运与原产地风险，直接</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -11233,17 +11233,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
+          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>转运与原产地风险，直接</t>
+          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -11464,12 +11464,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>WTO 对印 TPR 属东道国贸易政策环境证据，可用作建厂决策背景，但非全球投资趋势或企业供应链调查 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
         </is>
       </c>
     </row>
@@ -11541,44 +11541,44 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J144" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>中国对外投资规则，直接</t>
+          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
     </row>
@@ -11618,12 +11618,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>全球投资趋势，直接</t>
+          <t>中国对外投资规则，直接</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
     </row>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>欧盟外资安全审查框架，属‘投资政策’证据，可用于评估海外建厂面临的东道国审查风险</t>
+          <t>全球投资趋势，直接</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2019-03-21 Effective da</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
     </row>
@@ -12003,12 +12003,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>马来西亚/越南被认定‘未规避’的企业对照案例，可为‘泰国 vs 泰马分散’的市场准入比较提供参考，但属光伏行业类比 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>东南亚四国光伏反规避认定（含马来西亚）可作跨行业对照，说明马来西亚原产地同样受美方审查，但非电池/EV 案例 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -12146,10 +12146,3860 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：特斯拉 10-K 原文披露上海/柏林/美国制造布局与关税影响</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对华 EV 反补贴税，属整车厂关税暴露的同类政策背景，但不回答特斯拉自身披露 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知）</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>美国 Section 301 对华关税清单（含 EV 与锂电池），是特斯拉披露‘关税推高供应链成本’的政策依据 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） Publisher: 美国贸易代表办公室（USTR，Federal Register） Country/Jurisdiction: US / Federal Publication date: 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>强迫劳动清单与特斯拉制造布局/关税披露无关</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>电池装车量市场数据，不能回答企业制造布局披露 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：蔚来 20-F 披露三座中国制造基地与 BIS 对华半导体管制风险</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>XPEV_001</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>XPeng Inc. Form 20-F（fiscal year ended December 31, 2025）小鹏汽车2025财年年报</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：小鹏 20-F 披露肇庆/广州/武汉基地与出口管制采购风险</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: XPEV_001 Title: XPeng Inc. Form 20-F（fiscal year ended December 31, 2025）小鹏汽车2025财年年报 Publisher: 小鹏汽车（XPeng Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-16 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>FR_001</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Federal Register API（美国联邦公报）</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>出口管制/关税</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>美国联邦公报监测入口，可追踪出口管制/关税规则变化，属合规背景工具而非企业披露</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>美国国家档案馆联邦公报办公室</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>中国对美两用物项出口管制反制措施，可作中美出口管制互动的政策背景</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>商务部</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>ITA_001</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated Screening List API（美国合并筛查清单）</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>美国受限方筛查清单入口，可支持出口管制合规流程判断，但非企业披露</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>美国国际贸易管理局（ITA）</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J162" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：雅保 10-K 披露智利/澳大利亚资源与中澳加工布局及贸易政策风险</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 Publisher: 雅保公司（Albemarle Corporation，SEC EDGAR） Country/Jurisdiction: US/CL/AU/CN / Federal (SEC registrant) Publication date: 2026-02-11 Status: CURRENT Topic: 供应链布局 Appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>美国 UFLPA 清单含碳酸锂与电池铝箔实体，直接构成锂材料供应链的贸易/合规风险 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>全球电池装车量数据，可支撑锂盐需求侧判断，但不涉及雅保自身布局</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>转运执法报告，与锂资源/加工布局披露无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>美国 EV/锂电池进口数据，可作锂电材料贸易流背景</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：第4章原产地规则给出 75%/65% 区域成分门槛与劳动价值含量要求</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR）</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>强迫劳动合规与 USMCA 原产地门槛无关</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>转运可视化与执法分析，可支持‘原产地需可举证’的实施难度判断</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>战略与国际研究中心（CSIS）</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>电池市场数据与原产地门槛无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>美国 IRA 电池组件/关键矿物本地含量规则，属同类内容门槛，可用于对照但不适用于 USMCA ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：WTO 对印贸易政策审议，覆盖关税结构与本地化/投资审查基线</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>WTO_003</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度）</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J173" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：印度 2025 年 MFN 平均 16.0%、非农 12.8% 等关税量化数据</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2025-07 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: WTO国别</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>美国强迫劳动清单与印度准入基线无关</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>美国 IRA 本地含量规则，属同类本地化政策对照，但非印度规则 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>印尼贸易政策审议，属同类市场准入基线，可作区域对照但非印度数据 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：WTO 对印尼审议记载 TKDN 本地含量要求与镍矿出口禁令/下游化政策</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>强迫劳动清单与印尼本地含量/下游化要求无关</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>美国 IRA 电池本地含量规则，属同类本地化政策对照，但非印尼规则</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>欧盟电池法规的尽职调查与准入要求，属同类市场准入合规对照，但非印尼规则</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>电池装车量数据不能回答印尼的政策要求 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>After unwinding its joint venture with Ford and moving to sole operation of its Tennessee plant, the company is securing LFP materials for its North American ESS business and speeding up the search for demand beyond electric vehicles. Japan's Panasonic ranked sixth with 29. 7 GWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告）</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：世行 LPI 2023 给出中国/越南/印尼/墨西哥的物流与海关分项评分，是本题唯一可量化基准</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） Publisher: 世界银行（World Bank） Country/Jurisdiction: 全球 / Global Publication date: 2023-04-28 Status: CURRENT Topic: 物流 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>光伏反规避终裁与物流成本无关</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>美国自中/越/泰/马进口数据可估转移规模，但不含物流与通关效率指标</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>强迫劳动合规要求与物流成本无关</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>欧盟反补贴税属关税成本，非物流/通关效率</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I187" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J187" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：UFLPA 实体清单的可反驳推定直接限制电池材料供应商选择</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>IRA FEOC 规则以‘外国关注实体’限制电池组件/关键矿物资格，属同类合规约束 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>欧盟电池法规的供应链尽职调查义务，属同类合规要求（欧盟侧） ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>电池市场数据与强迫劳动合规无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>企业关税/供应链披露，不涉及强迫劳动合规 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：1–8 月装车量 844.2GWh、宁德时代 39.4%、中国七家合计 73.3%，直接量化集中度</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>强迫劳动清单不提供供给集中度数据</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>欧盟反补贴税属政策回应，不含集中度数据</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>IRA FEOC 规则属政策回应，不含集中度数据</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>欧盟电池法规属准入合规，与供给集中度无关</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：墨西哥侧的原产地成分门槛（原产地门槛维度）</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR）</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告）</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：中国/越南/印尼/墨西哥物流与海关评分（物流成本维度）</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） Publisher: 世界银行（World Bank） Country/Jurisdiction: 全球 / Global Publication date: 2023-04-28 Status: CURRENT Topic: 物流 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>美国 IRA 本地含量规则可作为‘迁往墨西哥后仍受美国内容门槛约束’的补充约束 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J200" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：印尼 TKDN 本地含量与下游化要求（本地含量维度）</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>光伏反规避判例与本题三个维度的取舍无关</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q151"/>
+  <autoFilter ref="A1:Q201"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:J151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12163,7 +16013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12255,11 +16105,11 @@
         <v>4</v>
       </c>
       <c r="D2" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A2,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A2,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A2,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A2,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F2" s="3" t="n">
@@ -12309,11 +16159,11 @@
         <v>2</v>
       </c>
       <c r="D3" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A3,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A3,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A3,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A3,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F3" s="3" t="n">
@@ -12363,11 +16213,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A4,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A4,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A4,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A4,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n">
@@ -12417,11 +16267,11 @@
         <v>5</v>
       </c>
       <c r="D5" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A5,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A5,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A5,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A5,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n">
@@ -12471,11 +16321,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A6,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A6,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A6,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A6,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F6" s="3" t="n">
@@ -12508,7 +16358,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -12525,11 +16375,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A7,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A7,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A7,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A7,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
@@ -12579,11 +16429,11 @@
         <v>4</v>
       </c>
       <c r="D8" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A8,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A8,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A8,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A8,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n">
@@ -12616,7 +16466,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -12630,14 +16480,14 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A9,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A9,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A9,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A9,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
@@ -12670,7 +16520,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001</t>
         </is>
       </c>
     </row>
@@ -12687,11 +16537,11 @@
         <v>4</v>
       </c>
       <c r="D10" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A10,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A10,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A10,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A10,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F10" s="3" t="n">
@@ -12741,11 +16591,11 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A11,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A11,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E11" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A11,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A11,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F11" s="3" t="n">
@@ -12778,7 +16628,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001</t>
+          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -12795,11 +16645,11 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A12,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A12,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E12" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A12,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A12,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F12" s="3" t="n">
@@ -12832,7 +16682,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -12849,11 +16699,11 @@
         <v>2</v>
       </c>
       <c r="D13" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A13,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A13,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E13" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A13,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A13,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F13" s="3" t="n">
@@ -12886,7 +16736,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007</t>
+          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004</t>
         </is>
       </c>
     </row>
@@ -12903,11 +16753,11 @@
         <v>5</v>
       </c>
       <c r="D14" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A14,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A14,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E14" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A14,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A14,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F14" s="3" t="n">
@@ -12957,11 +16807,11 @@
         <v>4</v>
       </c>
       <c r="D15" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A15,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A15,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E15" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A15,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A15,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F15" s="3" t="n">
@@ -12994,7 +16844,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -13011,11 +16861,11 @@
         <v>2</v>
       </c>
       <c r="D16" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A16,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A16,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E16" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A16,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A16,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n">
@@ -13065,11 +16915,11 @@
         <v>2</v>
       </c>
       <c r="D17" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A17,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A17,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E17" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A17,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A17,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F17" s="3" t="n">
@@ -13102,7 +16952,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001</t>
         </is>
       </c>
     </row>
@@ -13119,11 +16969,11 @@
         <v>4</v>
       </c>
       <c r="D18" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A18,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A18,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E18" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A18,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A18,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F18" s="3" t="n">
@@ -13156,7 +17006,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001</t>
         </is>
       </c>
     </row>
@@ -13170,14 +17020,14 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A19,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A19,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E19" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A19,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A19,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F19" s="3" t="n">
@@ -13210,7 +17060,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -13224,14 +17074,14 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A20,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A20,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E20" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A20,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A20,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F20" s="3" t="n">
@@ -13264,7 +17114,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -13281,11 +17131,11 @@
         <v>4</v>
       </c>
       <c r="D21" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A21,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A21,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E21" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A21,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A21,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F21" s="3" t="n">
@@ -13318,7 +17168,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001</t>
+          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001</t>
         </is>
       </c>
     </row>
@@ -13332,14 +17182,14 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A22,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A22,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E22" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A22,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A22,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F22" s="3" t="n">
@@ -13372,7 +17222,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -13389,11 +17239,11 @@
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A23,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A23,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E23" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A23,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A23,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F23" s="3" t="n">
@@ -13426,7 +17276,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001</t>
         </is>
       </c>
     </row>
@@ -13443,11 +17293,11 @@
         <v>5</v>
       </c>
       <c r="D24" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A24,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A24,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E24" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A24,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A24,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F24" s="3" t="n">
@@ -13480,7 +17330,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -13497,11 +17347,11 @@
         <v>5</v>
       </c>
       <c r="D25" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A25,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A25,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E25" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A25,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A25,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F25" s="3" t="n">
@@ -13548,14 +17398,14 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A26,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A26,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E26" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A26,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A26,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F26" s="3" t="n">
@@ -13588,7 +17438,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003</t>
         </is>
       </c>
     </row>
@@ -13605,11 +17455,11 @@
         <v>4</v>
       </c>
       <c r="D27" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A27,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A27,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E27" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A27,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A27,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F27" s="3" t="n">
@@ -13642,7 +17492,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001</t>
+          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -13659,11 +17509,11 @@
         <v>4</v>
       </c>
       <c r="D28" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A28,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A28,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E28" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A28,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A28,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F28" s="3" t="n">
@@ -13696,7 +17546,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -13713,11 +17563,11 @@
         <v>5</v>
       </c>
       <c r="D29" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A29,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A29,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E29" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A29,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A29,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F29" s="3" t="n">
@@ -13750,7 +17600,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010</t>
         </is>
       </c>
     </row>
@@ -13767,11 +17617,11 @@
         <v>3</v>
       </c>
       <c r="D30" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A30,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A30,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E30" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A30,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A30,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F30" s="3" t="n">
@@ -13804,7 +17654,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004</t>
+          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001</t>
         </is>
       </c>
     </row>
@@ -13821,11 +17671,11 @@
         <v>3</v>
       </c>
       <c r="D31" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A31,'Item Scoring'!$I$2:$I$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A31,'Item Scoring'!$I$2:$I$201),"")</f>
         <v/>
       </c>
       <c r="E31" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$151,$A31,'Item Scoring'!$J$2:$J$151),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A31,'Item Scoring'!$J$2:$J$201),"")</f>
         <v/>
       </c>
       <c r="F31" s="3" t="n">
@@ -13858,13 +17708,553 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A32,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A32,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>gold（TSLA_001）命中且排名第1，制造布局与关税影响可直接回答</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A33,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A33,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>三家 gold（NIO_001/XPEV_001/LI_001）全部命中，分别排名1–2</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A34,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A34,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>gold（ALB_001）命中且排名第1，锂资源/加工布局与贸易政策风险可答</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A35,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A35,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>gold（USMCA_001）命中且排名第1，75%/65% 原产地门槛可答</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A36,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A36,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>两份 India gold（WTO_002/WTO_003）全部命中，排名1–2（关税水平 + 政策基线）</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A37,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A37,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>gold（WTO_004）命中且排名第1，TKDN 本地含量与镍下游化要求可答</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A38,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A38,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>gold（WB_001）命中且排名第1，可给出中国/越南/印尼/墨西哥物流基准</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_002; TRD_001; DHS_001; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A39,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A39,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>gold（DHS_001）命中且排名第1，UFLPA 可反驳推定对电池材料的约束可答</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A40,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A40,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>仅 SNE_001 命中（排名第1），IEA_001 未进 Top-5，集中度证据覆盖不完整</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A41,'Item Scoring'!$I$2:$I$201),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A41,'Item Scoring'!$J$2:$J$201),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>三份 gold（USMCA_001/WB_001/WTO_004）全部命中，三个维度均有直接证据</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13939,7 +18329,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>AVERAGE('Question Scoring'!$D$2:$D$31)</f>
+        <f>AVERAGE('Question Scoring'!$D$2:$D$41)</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -13959,7 +18349,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>AVERAGE('Question Scoring'!$E$2:$E$31)</f>
+        <f>AVERAGE('Question Scoring'!$E$2:$E$41)</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -13979,7 +18369,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>AVERAGE('Question Scoring'!$B$2:$B$31)</f>
+        <f>AVERAGE('Question Scoring'!$B$2:$B$41)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -13999,7 +18389,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(AVERAGE('Question Scoring'!$F$2:$F$31),"")</f>
+        <f>IFERROR(AVERAGE('Question Scoring'!$F$2:$F$41),"")</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">

--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Rubric" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Scoring'!$A$1:$Q$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Scoring'!$A$1:$Q$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2705,25 +2705,25 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>BIS规则时间线合成案例，内容重复BIS_001/002</t>
+          <t>暂停措施涉及镓、锗、石墨，直接回答</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2782,25 +2782,25 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>暂停措施涉及镓、锗、石墨，直接回答</t>
+          <t>BIS规则时间线合成案例，内容重复BIS_001/002</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
     </row>
@@ -6613,44 +6613,44 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
+          <t>强迫劳动清单不能支持美国 EV/电池进口来源是否转移的判断</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -6690,44 +6690,44 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>强迫劳动清单不能支持美国 EV/电池进口来源是否转移的判断</t>
+          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
     </row>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
     </row>
@@ -15314,44 +15314,44 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>强迫劳动清单不提供供给集中度数据</t>
+          <t>美国自中/越/泰/马进口 EV(870380) 与锂电池(850760) 数据，可部分反映电池供给来源集中度（美国市场口径），但不提供全球份额</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="Q193" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
     </row>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>欧盟反补贴税属政策回应，不含集中度数据</t>
+          <t>强迫劳动清单不提供供给集中度数据</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="Q194" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -15468,17 +15468,17 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>IRA FEOC 规则属政策回应，不含集中度数据</t>
+          <t>欧盟反补贴税属政策回应，不含集中度数据</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="Q195" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
         </is>
       </c>
     </row>
@@ -15545,17 +15545,17 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>欧盟电池法规属准入合规，与供给集中度无关</t>
+          <t>IRA FEOC 规则属政策回应，不含集中度数据</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="Q196" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
     </row>
@@ -15996,10 +15996,1165 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I202" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：欧盟电池法规第 7/9/77 条（碳足迹、再生材料含量、尽职调查、电池护照）</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>美国 UFLPA 进口限制与欧盟电池合规要求属不同辖区/不同域</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对华纯电反补贴税属同一辖区(EU)的市场准入措施，可作欧盟侧贸易壁垒背景，但不回答电池产品合规要求 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>转运可视化分析，与欧盟电池产品合规要求无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>战略与国际研究中心（CSIS）</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>The EV battery example shows the problem that a product passport is designed to solve. At its simplest, a product passport is a digital record that travels with a good through its supply chain, showing where its inputs came from and whether it qualiﬁes for preferential treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>电池装车量市场数据，不回答合规要求</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：欧盟对华纯电最终反补贴税税率（BYD 17.0% / Geely 18.8% / SAIC 35.3% / Tesla 7.8% 等）</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>美国对东南亚光伏的反规避裁定，辖区与措施类型均不同</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>强迫劳动实体清单与欧盟反补贴税率无关</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>美国 EV/锂电池进口数据，不含欧盟税率信息；作为跨辖区贸易流数据不可用于本题计算 ｜ 人工判定与Auto(1)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>电池装车量数据与税率无关</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>EU_002</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA）</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：CRMA 本土开采 10%/加工 40%/回收 25% 目标与单一第三国 ≤65% 上限</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2024-05-03 E</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例）</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>本题 expected 证据：欧盟外资安全审查框架（成员国可按安全/公共秩序审查外资）</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2019-03-21 Effective da</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>美国强迫劳动清单与欧盟层面投资约束无关</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规）</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I215" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>欧盟电池法规的合规与尽责要求，属同一辖区监管约束，可补足建厂后的产品侧义务 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对华纯电反补贴税，属同一辖区贸易措施，影响对欧建厂/出口的成本判断 ｜ 人工判定与Auto(0)不同，请复核</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q201"/>
+  <autoFilter ref="A1:Q216"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:J216" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16013,7 +17168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16105,11 +17260,11 @@
         <v>4</v>
       </c>
       <c r="D2" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A2,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A2,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A2,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A2,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F2" s="3" t="n">
@@ -16159,11 +17314,11 @@
         <v>2</v>
       </c>
       <c r="D3" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A3,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A3,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A3,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A3,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F3" s="3" t="n">
@@ -16213,11 +17368,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A4,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A4,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A4,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A4,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n">
@@ -16267,11 +17422,11 @@
         <v>5</v>
       </c>
       <c r="D5" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A5,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A5,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A5,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A5,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n">
@@ -16321,11 +17476,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A6,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A6,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A6,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A6,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F6" s="3" t="n">
@@ -16375,11 +17530,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A7,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A7,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A7,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A7,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
@@ -16412,7 +17567,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -16429,11 +17584,11 @@
         <v>4</v>
       </c>
       <c r="D8" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A8,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A8,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A8,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A8,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n">
@@ -16483,11 +17638,11 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A9,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A9,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A9,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A9,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
@@ -16537,11 +17692,11 @@
         <v>4</v>
       </c>
       <c r="D10" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A10,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A10,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A10,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A10,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F10" s="3" t="n">
@@ -16591,11 +17746,11 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A11,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A11,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E11" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A11,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A11,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F11" s="3" t="n">
@@ -16645,11 +17800,11 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A12,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A12,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E12" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A12,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A12,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F12" s="3" t="n">
@@ -16699,11 +17854,11 @@
         <v>2</v>
       </c>
       <c r="D13" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A13,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A13,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E13" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A13,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A13,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F13" s="3" t="n">
@@ -16753,11 +17908,11 @@
         <v>5</v>
       </c>
       <c r="D14" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A14,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A14,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E14" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A14,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A14,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F14" s="3" t="n">
@@ -16807,11 +17962,11 @@
         <v>4</v>
       </c>
       <c r="D15" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A15,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A15,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E15" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A15,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A15,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F15" s="3" t="n">
@@ -16861,11 +18016,11 @@
         <v>2</v>
       </c>
       <c r="D16" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A16,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A16,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E16" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A16,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A16,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n">
@@ -16915,11 +18070,11 @@
         <v>2</v>
       </c>
       <c r="D17" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A17,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A17,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E17" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A17,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A17,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F17" s="3" t="n">
@@ -16952,7 +18107,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001</t>
+          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -16969,11 +18124,11 @@
         <v>4</v>
       </c>
       <c r="D18" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A18,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A18,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E18" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A18,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A18,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F18" s="3" t="n">
@@ -17023,11 +18178,11 @@
         <v>3</v>
       </c>
       <c r="D19" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A19,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A19,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E19" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A19,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A19,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F19" s="3" t="n">
@@ -17077,11 +18232,11 @@
         <v>3</v>
       </c>
       <c r="D20" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A20,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A20,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E20" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A20,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A20,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F20" s="3" t="n">
@@ -17131,11 +18286,11 @@
         <v>4</v>
       </c>
       <c r="D21" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A21,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A21,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E21" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A21,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A21,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F21" s="3" t="n">
@@ -17185,11 +18340,11 @@
         <v>4</v>
       </c>
       <c r="D22" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A22,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A22,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E22" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A22,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A22,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F22" s="3" t="n">
@@ -17239,11 +18394,11 @@
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A23,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A23,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E23" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A23,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A23,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F23" s="3" t="n">
@@ -17293,11 +18448,11 @@
         <v>5</v>
       </c>
       <c r="D24" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A24,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A24,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E24" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A24,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A24,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F24" s="3" t="n">
@@ -17347,11 +18502,11 @@
         <v>5</v>
       </c>
       <c r="D25" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A25,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A25,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E25" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A25,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A25,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F25" s="3" t="n">
@@ -17401,11 +18556,11 @@
         <v>3</v>
       </c>
       <c r="D26" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A26,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A26,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E26" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A26,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A26,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F26" s="3" t="n">
@@ -17455,11 +18610,11 @@
         <v>4</v>
       </c>
       <c r="D27" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A27,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A27,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E27" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A27,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A27,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F27" s="3" t="n">
@@ -17509,11 +18664,11 @@
         <v>4</v>
       </c>
       <c r="D28" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A28,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A28,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E28" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A28,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A28,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F28" s="3" t="n">
@@ -17563,11 +18718,11 @@
         <v>5</v>
       </c>
       <c r="D29" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A29,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A29,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E29" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A29,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A29,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F29" s="3" t="n">
@@ -17617,11 +18772,11 @@
         <v>3</v>
       </c>
       <c r="D30" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A30,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A30,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E30" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A30,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A30,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F30" s="3" t="n">
@@ -17671,11 +18826,11 @@
         <v>3</v>
       </c>
       <c r="D31" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A31,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A31,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E31" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A31,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A31,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F31" s="3" t="n">
@@ -17725,11 +18880,11 @@
         <v>1</v>
       </c>
       <c r="D32" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A32,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A32,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E32" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A32,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A32,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F32" s="3" t="n">
@@ -17779,11 +18934,11 @@
         <v>2</v>
       </c>
       <c r="D33" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A33,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A33,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E33" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A33,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A33,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F33" s="3" t="n">
@@ -17833,11 +18988,11 @@
         <v>1</v>
       </c>
       <c r="D34" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A34,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A34,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E34" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A34,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A34,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F34" s="3" t="n">
@@ -17887,11 +19042,11 @@
         <v>1</v>
       </c>
       <c r="D35" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A35,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A35,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E35" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A35,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A35,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F35" s="3" t="n">
@@ -17941,11 +19096,11 @@
         <v>2</v>
       </c>
       <c r="D36" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A36,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A36,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E36" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A36,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A36,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F36" s="3" t="n">
@@ -17995,11 +19150,11 @@
         <v>1</v>
       </c>
       <c r="D37" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A37,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A37,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E37" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A37,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A37,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F37" s="3" t="n">
@@ -18049,11 +19204,11 @@
         <v>1</v>
       </c>
       <c r="D38" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A38,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A38,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E38" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A38,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A38,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F38" s="3" t="n">
@@ -18103,11 +19258,11 @@
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A39,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A39,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E39" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A39,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A39,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F39" s="3" t="n">
@@ -18157,11 +19312,11 @@
         <v>1</v>
       </c>
       <c r="D40" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A40,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A40,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E40" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A40,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A40,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F40" s="3" t="n">
@@ -18194,7 +19349,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001</t>
+          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -18211,11 +19366,11 @@
         <v>3</v>
       </c>
       <c r="D41" s="2">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A41,'Item Scoring'!$I$2:$I$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A41,'Item Scoring'!$I$2:$I$216),"")</f>
         <v/>
       </c>
       <c r="E41" s="3">
-        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$201,$A41,'Item Scoring'!$J$2:$J$201),"")</f>
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A41,'Item Scoring'!$J$2:$J$216),"")</f>
         <v/>
       </c>
       <c r="F41" s="3" t="n">
@@ -18249,12 +19404,174 @@
       <c r="L41" s="2" t="inlineStr">
         <is>
           <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A42,'Item Scoring'!$I$2:$I$216),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A42,'Item Scoring'!$J$2:$J$216),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>gold（EU_001）命中且排名第1，欧盟电池法规合规要求可直接作答</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A43,'Item Scoring'!$I$2:$I$216),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A43,'Item Scoring'!$J$2:$J$216),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>gold（EU_003）命中且排名第1，各企业反补贴税率可直接作答</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="2">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A44,'Item Scoring'!$I$2:$I$216),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="3">
+        <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A44,'Item Scoring'!$J$2:$J$216),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>两份 gold（EU_002/EU_004）全部命中，分别排名第1–2</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; DHS_001; EU_001; EU_003</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18329,7 +19646,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>AVERAGE('Question Scoring'!$D$2:$D$41)</f>
+        <f>AVERAGE('Question Scoring'!$D$2:$D$44)</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -18349,7 +19666,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>AVERAGE('Question Scoring'!$E$2:$E$41)</f>
+        <f>AVERAGE('Question Scoring'!$E$2:$E$44)</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -18369,7 +19686,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>AVERAGE('Question Scoring'!$B$2:$B$41)</f>
+        <f>AVERAGE('Question Scoring'!$B$2:$B$44)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -18389,7 +19706,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(AVERAGE('Question Scoring'!$F$2:$F$41),"")</f>
+        <f>IFERROR(AVERAGE('Question Scoring'!$F$2:$F$44),"")</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">

--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>NIO_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
+          <t>Consolidated Screening List API（美国合并筛查清单）</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3635,19 +3635,19 @@
         <v>2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>企业年报披露半导体出口管制风险，不涉及关联企业规则暂停/恢复时间线 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>筛查数据源，对窗口风险为辅助</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Uncertai</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -6459,44 +6459,44 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>中国对越/泰/马中间品出口，直接</t>
+          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -6536,44 +6536,44 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>中国对越/泰/马中间品出口，直接</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -6690,22 +6690,22 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
@@ -6715,19 +6715,19 @@
         <v>2</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>同区域同模式的贸易转移数据（光伏组件），可作模式类比，非EV/电池口径</t>
+          <t>白宫非法转运报告，供应链迁移相关政策证据直接来源 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -7460,26 +7460,26 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>2</v>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>美国进口贸易数据，可作布局结果佐证，非风险隔离证据</t>
+          <t>FEOC 规则按「实体」而非「产地」判定补贴资格，直接说明把工序迁到东南亚并不等于切断中国实体暴露，与本题「迁移不能完全隔离风险」同向；非本题 gold ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Uncertai</t>
         </is>
       </c>
     </row>
@@ -10925,22 +10925,22 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>中国对东南亚中间品出口数据，可佐证‘迁移工序≠切断中间品依赖’，但本题核心是反规避/转运判例</t>
+          <t>加强海关执法的行政令，指向原产地与转运执法，是情景B（东南亚部分工序）执法风险的直接政策依据；非本题 gold</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -11233,17 +11233,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
+          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -11310,17 +11310,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
+          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
     </row>
@@ -12696,17 +12696,17 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报）</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>美国联邦公报监测入口，可追踪出口管制/关税规则变化，属合规背景工具而非企业披露</t>
+          <t>中国对美两用物项出口管制反制措施，可作中美出口管制互动的政策背景</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -12773,17 +12773,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>Federal Register API（美国联邦公报）</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>中国对美两用物项出口管制反制措施，可作中美出口管制互动的政策背景</t>
+          <t>美国联邦公报监测入口，可追踪出口管制/关税规则变化，属合规背景工具而非企业披露</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Uncertai</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="Q169" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -15314,44 +15314,44 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>美国自中/越/泰/马进口 EV(870380) 与锂电池(850760) 数据，可部分反映电池供给来源集中度（美国市场口径），但不提供全球份额</t>
+          <t>强迫劳动清单不提供供给集中度数据</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="Q193" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -15391,44 +15391,44 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>强迫劳动清单不提供供给集中度数据</t>
+          <t>美国自中/越/泰/马进口 EV(870380) 与锂电池(850760) 数据，可部分反映电池供给来源集中度（美国市场口径），但不提供全球份额</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="Q194" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="Q210" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; ITA_001</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002</t>
+          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18215,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003</t>
         </is>
       </c>
     </row>
@@ -18971,7 +18971,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>

--- a/Task2_manual_scoring_v3.xlsx
+++ b/Task2_manual_scoring_v3.xlsx
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>美国商务部反规避认定（含马来西亚企业），直接反映美方对马来西亚原产地的官方判断 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>美国商务部认定东南亚四国光伏视为中国原产，直接反映美方对马来西亚原产地的官方判断 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>美国商务部认定东南亚四国光伏视为中国原产，直接反映美方对马来西亚原产地的官方判断 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>美国商务部反规避认定（含马来西亚企业），直接反映美方对马来西亚原产地的官方判断 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -1300,26 +1300,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>2</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>中国对马/越/泰中间品出口数据，间接支持企业马来西亚布局判断</t>
+          <t>马来西亚投资环境官方指南（含党派之争、并购安全审查、国有化风险），为「在马来西亚布局」的国别风险背景；但本题问的是中国企业布局案例与美国官方对转运的判断，指南两者都不提供 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
+          <t>8. 中资企业在马开展投资合作应注意的问题 8.1 主要风险 （1）政治风险 相较于东南亚许多国家政权变动频繁、社会动荡、民族宗教问题突出、受恐怖主义 威胁，马来西亚政治风险较低，但也存在潜在的政治风险，包括逐渐激烈的党派之争、 美国对马来西亚的影响等。马来西亚实行多党制，由几个政党联合组成政党联盟执政， 虽然马来西亚政局总体平稳发展，但近年来政治斗争不断加剧。执政党、反对党和公民 社会三方的良性互动是马来西亚局势稳定的关键。 （2）环境保护风险 马来西亚目前没有统一的环保法典，环保法律体系相对复杂，由众多法律、法规、 条例组成。在一项可能对环境造成影响</t>
         </is>
       </c>
     </row>
@@ -2455,44 +2455,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚转运高风险并推AI执法，直接说明认定规避的官方立场</t>
+          <t>印度订单回流案例，与规避/未规避认定无关 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>暂停令，直接回答暂停措施</t>
+          <t>暂停措施涉及镓、锗、石墨，直接回答</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>50%穿透规则原文，直接回答美方规则</t>
+          <t>暂停令，直接回答暂停措施</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>暂停措施涉及镓、锗、石墨，直接回答</t>
+          <t>50%穿透规则原文，直接回答美方规则</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
         </is>
       </c>
     </row>
@@ -3918,44 +3918,44 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>光伏反规避判例，同类原产地执法先例</t>
+          <t>AI识别转运的可见性缺口分析，直接</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -3995,44 +3995,44 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>AI识别转运的可见性缺口分析，直接</t>
+          <t>光伏反规避判例，同类原产地执法先例</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版）</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4476,25 +4476,25 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>中国对外投资官方规则，直接</t>
+          <t>商务部《对外投资合作国别（地区）指南》属本题所问的「官方对外投资产品 + 东道国投资环境证据」，可直接支撑立项尽调；但本题 gold 指向中国对外投资制度（CNGOV_001）与国际组织证据（IMF/UNCTAD），国别指南为按国别补充，故记部分相关</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健 全海外综合服务体系，促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚 持统筹发展和安全，鼓励和支持有实力、信誉好、有国际竞争力的企业开展产供链国际 合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复 杂激烈，单边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的 新一代技术革命和产业变革深入发展，为国际经贸合作注入新动能、创造新</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4549,29 +4549,29 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>地缘经济碎片化框架，国际投资环境证据，直接</t>
+          <t>同上：越南国别指南，国别层次的投资环境/合规证据，非本题 gold 的中国制度与国际组织证据</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健全海外综合服务体系， 促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚持统筹发展和安全，鼓励和支持有 实力、信誉好、有国际竞争力的企业开展产供链国际合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复杂激烈，单 边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的新一代技术革命和产业 变革深入发展，为国际经贸合作注入新动能、创造新模</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版）</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4626,29 +4626,29 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>世界投资报告，国际投资环境直接证据</t>
+          <t>同上：泰国国别指南，国别层次的投资环境/合规证据，非本题 gold 的中国制度与国际组织证据</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健 全海外综合服务体系，促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚 持统筹发展和安全，鼓励和支持有实力、信誉好、有国际竞争力的企业开展产供链国际 合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复 杂激烈，单边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的 新一代技术革命和产业变革深入发展，为国际经贸合作注入新动能、创造新</t>
         </is>
       </c>
     </row>
@@ -4688,44 +4688,44 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>国务院关于对外投资的规定（国务院令第837号）</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>企业放弃海外建厂个案，可作立项风险实例，非制度/环境证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>中国对外投资官方规则，直接</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
         </is>
       </c>
     </row>
@@ -4765,17 +4765,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4784,25 +4784,25 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>既非中国对外投资规则，也非国际投资环境证据</t>
+          <t>同上：马来西亚国别指南，国别层次的投资环境/合规证据，非本题 gold 的中国制度与国际组织证据</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健 全海外综合服务体系，促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚 持统筹发展和安全，鼓励和支持有实力、信誉好、有国际竞争力的企业开展产供链国际 合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复 杂激烈，单边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的 新一代技术革命和产业变革深入发展，为国际经贸合作注入新动能、创造新</t>
         </is>
       </c>
     </row>
@@ -4842,17 +4842,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4861,25 +4861,25 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>WTO 对印贸易政策审议属官方贸易政策环境证据，可用作碎片化的国别佐证，但非国际组织宏观/投资证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>地缘经济对抗列为首要风险，直接</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
     </row>
@@ -4919,17 +4919,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版）</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4938,25 +4938,25 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>地缘经济对抗列为首要风险，直接</t>
+          <t>WTO 对印贸易政策审议属官方贸易政策环境证据，可用作碎片化的国别佐证，但非国际组织宏观/投资证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5011,29 +5011,29 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>动荡期FDI趋势，直接</t>
+          <t>越南国别指南反映的是东道国政治与营商环境的「现状描述」，可作为投资环境支撑，但不构成国际组织对地缘经济碎片化的分析（本题 gold 为 IMF/MCK/UNCTAD/WEF）；人工判定与Auto(0)口径不同请复核——本题主题桶为 investment_policy，指南 topic=对外投资</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
+          <t>4. 投资环境 4.1 投资吸引力 【主要优势】越南吸引外资的主要优势：一是政局稳定，经济发展较快。越南政 府执政能力较强，政策具有连续性，注重经济建设和改善民生；二是劳动力成本 相对 较低；三是地理位置优越，位于中南半岛东部，海岸线长达 3260公里，港口众多，运 输便利。北部与中国接壤，凭借地理优势与中国保持产业链和供应链深度融合；四是 政策法规相对宽松，为外国投资者提供较全面的法律保障和较大力度的优惠政策；五 是对外开放程度较高，已签署17项自贸协定，另有2项自贸协定谈判正在推进中，投资 者可利用RCEP、中国—东盟自贸区等平台开拓更广阔的国际市场</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号）</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5088,29 +5088,29 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>中国国内规定，非国际组织证据</t>
+          <t>动荡期FDI趋势，直接</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
         </is>
       </c>
     </row>
@@ -5150,26 +5150,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版）</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>2</v>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>WTO 对印尼贸易政策审议，同上：国别贸易政策环境证据，非全球宏观趋势证据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>泰国国别指南，同上：国别投资环境支撑，非国际组织层面的碎片化证据</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>122 Indonesia Investments, Holding Company for Indonesia's State-Owned Miners Ready in Q1-2017. Viewed at: https://www. indonesia-investments. com/news/todays-headlines/holding-company-for-indonesia-s- state-owned-miners-ready-in-q1-2017/item7541; and Deloitte, 2019-20 Investment</t>
+          <t>泰国（2025 年版） 寄语 泰国位于东盟中心位置，区位优势明显，社会总体较为稳定，政策透明度和贸易自 由化程度较高， 法律法规较为健全， 营商环境开放包容，2024年泰国国内生产总值为5263 亿美元，是东盟第三大经济体。 泰国商品在东盟国家享受零关税待遇，对周边国家具有 较强辐射能力。 泰国投资促进政策以“泰国4. 0”战略为核心，重点支持发展新型汽车、智能电子、 农业与生物科技、食品加工、高端旅游和康养、自动化、航空与物流、综合医疗、生物 燃料和化学工业、数字经济、国防工业、人力教育等12大目标产业。 近年来，为增强产 供链韧性、 应对国际贸易挑战</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则）</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6330,19 +6330,19 @@
         <v>2</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>规则内容，非入口</t>
+          <t>蔚来 20-F 既不是美国新规监测入口，也不是受限方筛查数据源；本题两类信息需求都不满足 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL</t>
+          <t>Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key</t>
         </is>
       </c>
     </row>
@@ -6459,17 +6459,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -6484,19 +6484,19 @@
         <v>2</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>强迫劳动清单不能支持美国 EV/电池进口来源是否转移的判断</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -6536,44 +6536,44 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>中国对越/泰/马中间品出口，直接</t>
+          <t>反规避「未规避」判例，涉及区域原产地认定，间接相关 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
     </row>
@@ -6613,44 +6613,44 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>强迫劳动清单不能支持美国 EV/电池进口来源是否转移的判断</t>
+          <t>中国对越/泰/马中间品出口，直接</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
     </row>
@@ -7460,17 +7460,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>FEOC 规则按「实体」而非「产地」判定补贴资格，直接说明把工序迁到东南亚并不等于切断中国实体暴露，与本题「迁移不能完全隔离风险」同向；非本题 gold ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>越南指南提示「政局稳定/政策连续」但要求投资前做政治与商业风险评估、劳务与合规合规成本，可作为「仅迁最终环节仍需承担东道国制度性风险」的辅助论据；非本题 gold ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健全海外综合服务体系， 促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚持统筹发展和安全，鼓励和支持有 实力、信誉好、有国际竞争力的企业开展产供链国际合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复杂激烈，单 边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的新一代技术革命和产业 变革深入发展，为国际经贸合作注入新动能、创造新模</t>
         </is>
       </c>
     </row>
@@ -7768,44 +7768,44 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>反规避判例，属监管风险证据，非供应链韧性/执行风险主体 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>东南亚建厂规避客户风险，直接说明布局调整</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
     </row>
@@ -7845,12 +7845,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等）</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>东南亚建厂规避客户风险，直接说明布局调整</t>
+          <t>特斯拉 10-K 披露全球产能与供应链风险，可作为「大企业持续调整供应链布局」的补充证据；但本题 gold 为中国企业海外扩产案例与企业供应链调查（KPMG_001）</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
+          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8172,25 +8172,25 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：美国自中/越/泰/马进口 EV 与锂电池数据，直接支撑地理集中度评估</t>
+          <t>全球贸易展望，提供宏观背景，非集中度/转运审查直接证据</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
+          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -8249,25 +8249,25 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，提供宏观背景，非集中度/转运审查直接证据</t>
+          <t>本题 expected 证据：美国自中/越/泰/马进口 EV 与锂电池数据，直接支撑地理集中度评估</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>点名东南亚转运高风险，直接</t>
+          <t>AI识别虚假原产地，直接</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>AI识别虚假原产地，直接</t>
+          <t>点名东南亚转运高风险，直接</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
+          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -8480,25 +8480,25 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>白宫转运报告，直接</t>
+          <t>USMCA 原产地成分门槛可作为‘原产地需实质举证’的同类规则参照，但本题聚焦美方对东南亚转运与原产地的执法</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -8557,25 +8557,25 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J105" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>USMCA 原产地成分门槛可作为‘原产地需实质举证’的同类规则参照，但本题聚焦美方对东南亚转运与原产地的执法</t>
+          <t>白宫转运报告，直接</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
     </row>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>暂停令，直接回答时间判断</t>
+          <t>完整时间线，直接</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
     </row>
@@ -8846,17 +8846,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -8865,25 +8865,25 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>完整时间线，直接</t>
+          <t>UFLPA 清单不是美国出口管制受限方清单，与受限方筛查流程无关</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -8923,17 +8923,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年）</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8942,25 +8942,25 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>UFLPA 清单不是美国出口管制受限方清单，与受限方筛查流程无关</t>
+          <t>暂停令，直接回答时间判断</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
     </row>
@@ -9077,12 +9077,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>“认定规避”判例，直接</t>
+          <t>官方反规避终裁原文，直接</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9154,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>官方反规避终裁原文，直接</t>
+          <t>“认定规避”判例，直接</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -9385,12 +9385,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则）</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -9404,25 +9404,25 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>东南亚转运高风险，直接</t>
+          <t>北美三边原产地规则与美方对东南亚光伏的反规避认定不属同一制度与产业，不构成对本题的借鉴 ｜ 人工判定与Auto(1)不同，请复核</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
         </is>
       </c>
     </row>
@@ -10078,26 +10078,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>2</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>WTO 对印贸易政策审议可作国别贸易政策环境证据，但非全球宏观需求/投资环境证据</t>
+          <t>马来西亚国别投资环境指南可支撑「进入海外市场如何理解外部环境」，但本题问的是全球贸易放缓/战略行业投资的宏观证据（IMF/MCK/UNCTAD/WEF/WTO）；人工判定与Auto(0)不同请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用</t>
+          <t>4. 投资环境 4.1 投资吸引力 马来西亚政府欢迎和鼓励外国投资者对其制造业及相关服务业进行投资，近年来一 直致力于改善投资环境、完善投资法律、加强投资激励，以吸引外资进入马来西亚的相 关行业。由于马来西亚投资法律体系完备、与国际通行标准接轨、各行业操作流程较为 规范，加之其独特的地缘优势，吸引了包括中国在内的各国企业赴马来西亚投资经营。 马来西亚投资环境的竞争优势主要体现在五个方面：地理位置优越，位于东南亚核 心地带，可成为进入东盟市场和前往中东澳新的桥梁；经济基础稳固，经济增长前景较 好；原材料资源丰富；人力资源素质较高，工资成本较低；民族关系融洽</t>
         </is>
       </c>
     </row>
@@ -10155,26 +10155,26 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>WTO_003</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度）</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>2</v>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>WTO 印度关税快照可作国别准入环境数据，但非全球宏观趋势证据</t>
+          <t>越南国别投资环境指南，同上：可作国别环境支撑，非宏观证据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2025-07 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: WTO国别</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健全海外综合服务体系， 促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚持统筹发展和安全，鼓励和支持有 实力、信誉好、有国际竞争力的企业开展产供链国际合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复杂激烈，单 边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的新一代技术革命和产业 变革深入发展，为国际经贸合作注入新动能、创造新模</t>
         </is>
       </c>
     </row>
@@ -10463,44 +10463,44 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>金属铸造回流案例，与BIS规则情景无关</t>
+          <t>蔚来 20-F 披露 BIS 对华半导体/出口管制风险与客户准入影响，可作为「依赖美国客户的制造企业」在 BIS 规则情景下的公司侧佐证；非两种情景的直接规则依据</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key</t>
         </is>
       </c>
     </row>
@@ -11233,17 +11233,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>2</v>
@@ -11265,12 +11265,12 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
+          <t>反规避终裁，界定“实质性转变”，直接 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
     </row>
@@ -11310,17 +11310,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南）</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>反规避「未规避」判例，直接支持「提高当地供应商比例」的可行性与原产地判断</t>
+          <t>本题 expected 证据：白宫点名东南亚为转运高风险并推出 AI 执法工具</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
     </row>
@@ -11387,17 +11387,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -11406,25 +11406,25 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J142" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>投资与碎片化框架，直接</t>
+          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
     </row>
@@ -11541,17 +11541,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -11560,25 +11560,25 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J144" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>全球贸易展望，非投资政策/调查证据 ｜ 人工判定与Auto(0)不同，请复核 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>投资与碎片化框架，直接</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
     </row>
@@ -12003,26 +12003,26 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>2</v>
@@ -12035,12 +12035,12 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>东南亚四国光伏反规避认定（含马来西亚）可作跨行业对照，说明马来西亚原产地同样受美方审查，但非电池/EV 案例 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>美国侧中国转运可视化的执法分析，对应本题「美国转运执法」这一比较维度；但该文以美墨加（USMCA）为落点，非东南亚单一/分散布局的直接案例</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
     </row>
@@ -13158,22 +13158,22 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G165" s="2" t="n">
@@ -13183,19 +13183,19 @@
         <v>2</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>转运执法报告，与锂资源/加工布局披露无关 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>美国 EV/锂电池进口数据，可作锂电材料贸易流背景</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -13235,44 +13235,44 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税）</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>美国 EV/锂电池进口数据，可作锂电材料贸易流背景</t>
+          <t>欧盟对华整车反补贴税率与雅保锂资源/转化加工的全球布局无关（跨主体、跨主题）</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
+          <t>_x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appellate Body Report, United States – Final Countervailing Duty Determination with Respect to Certain Softwood Lumber from Canada , WT/DS257/AB/R, para. 102. See recital (492), and in particular footnote 72, whi</t>
         </is>
       </c>
     </row>
@@ -13851,17 +13851,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -13876,19 +13876,19 @@
         <v>2</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J174" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>美国强迫劳动清单与印度准入基线无关</t>
+          <t>美国 IRA 本地含量规则，属同类本地化政策对照，但非印度规则 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="Q174" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G175" s="2" t="n">
@@ -13960,12 +13960,12 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>美国 IRA 本地含量规则，属同类本地化政策对照，但非印度规则 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>印尼贸易政策审议，属同类市场准入基线，可作区域对照但非印度数据 ｜ 人工判定与Auto(0)不同，请复核</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="Q175" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
         </is>
       </c>
     </row>
@@ -14005,22 +14005,22 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
@@ -14030,19 +14030,19 @@
         <v>2</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>印尼贸易政策审议，属同类市场准入基线，可作区域对照但非印度数据 ｜ 人工判定与Auto(0)不同，请复核</t>
+          <t>美国强迫劳动清单与印度准入基线无关</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Q176" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -14159,17 +14159,17 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -14178,25 +14178,25 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J178" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>强迫劳动清单与印尼本地含量/下游化要求无关</t>
+          <t>美国 IRA 电池本地含量规则，属同类本地化政策对照，但非印尼规则</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="Q178" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
     </row>
@@ -14236,17 +14236,17 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则）</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -14255,25 +14255,25 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>美国 IRA 电池本地含量规则，属同类本地化政策对照，但非印尼规则</t>
+          <t>强迫劳动清单与印尼本地含量/下游化要求无关</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="Q179" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -14390,44 +14390,44 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报）</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>电池装车量数据不能回答印尼的政策要求 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>马来西亚投资环境指南：国家与主题均不符（本题问印尼镍本地含量与下游化要求）</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="Q181" s="2" t="inlineStr">
         <is>
-          <t>After unwinding its joint venture with Ford and moving to sole operation of its Tennessee plant, the company is securing LFP materials for its North American ESS business and speeding up the search for demand beyond electric vehicles. Japan's Panasonic ranked sixth with 29. 7 GWh</t>
+          <t>庭和企业安装屋顶太阳能， 多余电力可售回电网； 能源效率提升， 工业节能， 目标到2040 年工业能耗降低11%，建筑节能，推广绿色建筑标准（如GBI认证）和智能电网技术； 低 碳交通，电动汽车（EV）推广，目标到2030年EV占新车销量的15%； 提供进口税减免、 充电桩建设补贴等支持； 氢能与碳捕集，目标2030年建成低碳氢中心，2050年成为区域 氢能供应国， 计划2030年前建设3个氢能与碳捕集枢纽， 年储存能力1500万吨； 绿色金融 与投资，2023年设立国家能源转型基金，初始拨款20亿令吉，支持脱碳项目，鼓励私人 资本投资可再生能源和储能项</t>
         </is>
       </c>
     </row>
@@ -14621,44 +14621,44 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>美国自中/越/泰/马进口数据可估转移规模，但不含物流与通关效率指标</t>
+          <t>强迫劳动合规要求与物流成本无关</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
     </row>
@@ -14698,44 +14698,44 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告）</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J185" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>强迫劳动合规要求与物流成本无关</t>
+          <t>美国自中/越/泰/马进口数据可估转移规模，但不含物流与通关效率指标</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="Q185" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
     </row>
@@ -15160,17 +15160,17 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
         <v>2</v>
@@ -15192,12 +15192,12 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>企业关税/供应链披露，不涉及强迫劳动合规 ｜ 人工判定与Auto(1)不同，请复核</t>
+          <t>中国侧两用物项出口管制公告，与美方强迫劳动合规（UFLPA/DHS）无关，属跨辖区跨主题噪声</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="Q191" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
     </row>
@@ -15853,44 +15853,44 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J200" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>本题 expected 证据：印尼 TKDN 本地含量与下游化要求（本地含量维度）</t>
+          <t>光伏反规避判例与本题三个维度的取舍无关</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="Q200" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
     </row>
@@ -15930,44 +15930,44 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H201" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J201" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>光伏反规避判例与本题三个维度的取舍无关</t>
+          <t>本题 expected 证据：印尼 TKDN 本地含量与下游化要求（本地含量维度）</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="Q201" s="2" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
         </is>
       </c>
     </row>
@@ -17351,7 +17351,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003</t>
+          <t>CASE_007; CASE_010; CASE_002; CASE_003; MOFCOM_004</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17473,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A6,'Item Scoring'!$I$2:$I$216),"")</f>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_010</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001</t>
+          <t>MOFCOM_002; BIS_002; BIS_001; CASE_009; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -17797,7 +17797,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A12,'Item Scoring'!$I$2:$I$216),"")</f>
@@ -17837,7 +17837,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_006; CNGOV_001; MOFCOM_004</t>
         </is>
       </c>
     </row>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006</t>
         </is>
       </c>
     </row>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; NIO_001</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002</t>
+          <t>TRD_001; DHS_001; CASE_003; TRD_003; WH_002</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18215,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; MOFCOM_003</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001</t>
+          <t>TRD_003; WH_002; CSIS_001; WTO_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001</t>
+          <t>CSIS_001; CASE_010; USMCA_001; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001</t>
+          <t>BIS_001; CASE_009; DHS_001; BIS_002; EU_001</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A24,'Item Scoring'!$I$2:$I$216),"")</f>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; NIO_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2">
         <f>IFERROR(AVERAGEIF('Item Scoring'!$A$2:$A$216,$A29,'Item Scoring'!$I$2:$I$216),"")</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003</t>
+          <t>TRD_003; CASE_002; WH_002; DOC_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001</t>
+          <t>WTO_001; WTO_002; IMF_001; CNGOV_001; UNCTAD_001</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18863,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001</t>
+          <t>ALB_001; DHS_001; SNE_001; TRD_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004</t>
+          <t>WTO_002; WTO_003; IRS_001; WTO_004; DHS_001</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001</t>
+          <t>WTO_004; IRS_001; DHS_001; EU_001; MOFCOM_004</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_002; TRD_001; DHS_001; EU_003</t>
+          <t>WB_001; CASE_002; DHS_001; TRD_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002</t>
+          <t>USMCA_001; WB_001; IRS_001; CASE_002; WTO_004</t>
         </is>
       </c>
     </row>
